--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$434</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$435</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G434"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -12785,12 +12785,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12814,12 +12814,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12843,12 +12843,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Ballast Mats(future Line)</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12872,12 +12872,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12901,12 +12901,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12930,12 +12930,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12959,12 +12959,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12988,12 +12988,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -13017,12 +13017,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -13046,12 +13046,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -13075,12 +13075,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -13104,12 +13104,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -13133,12 +13133,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -13162,12 +13162,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -13191,12 +13191,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -13220,12 +13220,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -13249,12 +13249,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -13278,12 +13278,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Control Point</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -13307,12 +13307,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -13336,12 +13336,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -13365,12 +13365,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -13394,12 +13394,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Fujirah Station</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -13423,12 +13423,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13448,24 +13448,24 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13485,24 +13485,24 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>HJR19A</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -13512,34 +13512,34 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>HJR19B</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>CH 50+942</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -13549,34 +13549,34 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>CH 55+041</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -13586,34 +13586,34 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -13638,19 +13638,19 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>CH 55+041</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -13660,34 +13660,34 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Fujairah</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Fujirah-New</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -13712,36 +13712,44 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13761,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -13770,7 +13778,7 @@
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 00+250</t>
+          <t>CH 01+100</t>
         </is>
       </c>
     </row>
@@ -13782,24 +13790,24 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+250</t>
         </is>
       </c>
     </row>
@@ -13811,24 +13819,24 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 00+000</t>
         </is>
       </c>
     </row>
@@ -13840,24 +13848,24 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00250</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 00+250</t>
+          <t>CH 01+100</t>
         </is>
       </c>
     </row>
@@ -13869,24 +13877,24 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00250</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 02+785</t>
+          <t>CH 00+250</t>
         </is>
       </c>
     </row>
@@ -13898,24 +13906,24 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 02+266</t>
+          <t>CH 02+785</t>
         </is>
       </c>
     </row>
@@ -13927,51 +13935,51 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Liwa</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>CH 02+266</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>CH 28+414</t>
-        </is>
-      </c>
+      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -13981,24 +13989,24 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CH 28+425</t>
+          <t>CH 28+414</t>
         </is>
       </c>
     </row>
@@ -14010,29 +14018,58 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
+          <t>CH 28+425</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
           <t>CH 29+500</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G434"/>
+  <autoFilter ref="A1:G435"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$435</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$441</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -13423,12 +13423,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -13443,29 +13443,29 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>HJR19A</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>HJR19B</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>CH 50+942</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Fin_Tamping</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -13554,24 +13554,24 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>CH 50+200</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -13596,19 +13596,19 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -13633,24 +13633,24 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -13665,29 +13665,29 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -13702,29 +13702,29 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -13739,82 +13739,98 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>FPJ 01A</t>
+        </is>
+      </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 00+250</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13824,7 +13840,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -13832,18 +13848,26 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -13853,26 +13877,34 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -13882,48 +13914,64 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00250</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>CODE-3</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 00+250</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 02+785</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13935,24 +13983,24 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CH 02+266</t>
+          <t>CH 01+100</t>
         </is>
       </c>
     </row>
@@ -13964,27 +14012,31 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>CH 00+250</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13994,26 +14046,26 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CH 28+414</t>
+          <t>CH 00+000</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14023,26 +14075,26 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
-          <t>CH 28+425</t>
+          <t>CH 01+100</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -14052,24 +14104,194 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2414-GMC-GQC-IR-00250</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
+          <t>CH 00+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00245</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>CH 02+785</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00254</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>CH 02+266</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00247</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00360</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>CH 28+414</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>CH 28+425</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
           <t>CH 29+500</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G435"/>
+  <autoFilter ref="A1:G441"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$441</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$438</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G441"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -13682,12 +13682,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -13719,12 +13719,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -13739,29 +13739,29 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -13776,17 +13776,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -13813,17 +13813,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13860,88 +13860,72 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 01+100</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 00+250</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -13951,7 +13935,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -13959,19 +13943,11 @@
           <t>UR</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 00+000</t>
         </is>
       </c>
     </row>
@@ -13983,12 +13959,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -14012,17 +13988,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00250</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
@@ -14041,24 +14017,24 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 02+785</t>
         </is>
       </c>
     </row>
@@ -14070,24 +14046,24 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 02+266</t>
         </is>
       </c>
     </row>
@@ -14099,12 +14075,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00250</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -14114,26 +14090,22 @@
       </c>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>CH 00+250</t>
-        </is>
-      </c>
+      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14145,153 +14117,70 @@
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
-          <t>CH 02+785</t>
+          <t>CH 28+414</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
-          <t>CH 02+266</t>
+          <t>CH 28+425</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>CH 28+414</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>CH 28+425</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr">
+      <c r="G438" t="inlineStr">
         <is>
           <t>CH 29+500</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G441"/>
+  <autoFilter ref="A1:G438"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -12936,7 +12936,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -498,7 +498,9 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://tristar.rdrive.io/p2225/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1821,7 +1823,9 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://tristar.rdrive.io/p2225/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -8354,7 +8358,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -12936,7 +12940,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -14076,7 +14080,9 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -14105,7 +14111,9 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -14134,7 +14142,9 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -14163,7 +14173,9 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -14192,7 +14204,9 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -14221,7 +14235,9 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -14250,7 +14266,9 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -14279,7 +14297,9 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -498,9 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://tristar.rdrive.io/p2225/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1823,9 +1821,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://tristar.rdrive.io/p2225/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12940,7 +12936,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -14080,9 +14076,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -14111,9 +14105,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -14142,9 +14134,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -14173,9 +14163,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -14204,9 +14192,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -14235,9 +14221,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -14266,9 +14250,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -14297,9 +14279,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://nicc.rdrive.io/p2414/processes?subcategory-ids=GHNN3EEF", waiting until "load"</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -12625,7 +12625,11 @@
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
@@ -12936,7 +12940,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -13627,12 +13631,12 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未搜到</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13738,12 +13742,12 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未搜到</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -12935,12 +12935,12 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00001-66</t>
+          <t>P2216-S04-GQC-IR-00166-00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00001-65</t>
+          <t>P2216-S04-GQC-IR-00165-00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>未搜到</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>未搜到</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$383</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12496,1889 +12496,8 @@
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>SURVEY WORK</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00155-00</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>Qty:5</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>SURVEY WORK</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00151-00</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Qty:4</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Structure gauge inspection</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00158-00</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>11+521 ~ 12+160</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Structure gauge inspection</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00160-00</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr"/>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00144-00</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00145-00</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00146-00</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr"/>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00147-00</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00148-00</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00149-00</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00150-00</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00152-00</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00153-00</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00154-00</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Fouling point</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00166-00</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>CH 10+425.000 ~ CH 12+160.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Fouling point</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00165-00</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>CH 10+425.000 ~ CH 12+160.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>CH 00+087</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Ballast Mats(future Line)</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>00+296</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>MFBW</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>CH 00+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Turnout 1st Tamping</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Turnout 2nd Tamping</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Turnout 3rd Tamping</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Turnout Final Tamping</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>-CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Turnout De-stressing</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>CH 52+426</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>De-streesing Of Rail</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>1sttamping</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>2nd Tamping</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>3rd Tamping</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Final Tamping</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Ballast Profilling</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Control Point</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>4 CONTROL POINT</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Fujairah Clearance And Fouling Marker</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00164-00</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00130</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Ballast Mat</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>ballast mat</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>FPJ 01A</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>1st_tamping</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>1st_Tamping</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>2nd_tamping</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>2nd_Tamping</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Fin_tamping</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>Fin_Tamping</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>CH 01+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>CH 00+250</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>CH 01+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00250</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>CODE-3</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>CH 00+250</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Existing Track Ramoval</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>CH 02+785</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Existing Track Ramoval</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>CH 02+266</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>CODE-3</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>CH 28+414</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>CH 28+425</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>CH 29+500</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G444"/>
+  <autoFilter ref="A1:G383"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$444</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G383"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12496,8 +12496,1889 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SURVEY WORK</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00155-00</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Qty:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SURVEY WORK</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00151-00</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Qty:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Structure gauge inspection</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00158-00</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>11+521 ~ 12+160</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Structure gauge inspection</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00160-00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00144-00</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00145-00</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00146-00</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00147-00</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00148-00</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00149-00</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00150-00</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00152-00</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00153-00</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00154-00</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Fouling point</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00166-00</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>CH 10+425.000 ~ CH 12+160.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Fouling point</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00165-00</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>CH 10+425.000 ~ CH 12+160.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00004-00</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00005-00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>CH 00+087</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Ballast Mats(future Line)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00157-00</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>00+296</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00006-00</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00008-00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>CH 00+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Turnout 1st Tamping</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00009-00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Turnout 2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00010-00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Turnout 3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00011-00</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Turnout Final Tamping</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00012-00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00013-00</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Turnout De-stressing</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00014-00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>CH 52+426</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>De-streesing Of Rail</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00015-00</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>1sttamping</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00016-00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00017-00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00018-00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00019-00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>4 CONTROL POINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Fujairah Clearance And Fouling Marker</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00164-00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Structural Gauge</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00168-00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Track Maker</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00170-00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Buffer Stop</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00130</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>未匹配到对应code</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>HJR19A</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>HJR19B</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>CH 50+942</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ballast Mat</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>未匹配到对应code</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>FPJ 01A</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1st_tamping</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>1st_Tamping</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2nd_tamping</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>2nd_Tamping</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Fin_tamping</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00243</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>CH 01+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00251</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>CH 00+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00253</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00244</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>CH 01+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00250</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>CH 00+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00245</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>CH 02+785</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00254</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>CH 02+266</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00247</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00360</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>CH 28+414</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>CH 28+425</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>CH 29+500</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G383"/>
+  <autoFilter ref="A1:G444"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -5734,7 +5734,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$378</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -12363,2022 +12363,8 @@
       </c>
       <c r="G378" t="inlineStr"/>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00162-00</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00163-00</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>12+130</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Existing track removal (JBL</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00029-00</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Existing track removal (JBL</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00030-00</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Existing track removal (JBL</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00031-00</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>04+250 ~ 04+331.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>SURVEY WORK</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00155-00</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>Qty:5</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>SURVEY WORK</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00151-00</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Qty:4</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Structure gauge inspection</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00158-00</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>11+521 ~ 12+160</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Structure gauge inspection</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00160-00</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr"/>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00144-00</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00145-00</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00146-00</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr"/>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00147-00</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>DTS 1st</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00148-00</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00149-00</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00150-00</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00152-00</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00153-00</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>DTS 2nd</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00154-00</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Fouling point</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00166-00</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>CH 10+425.000 ~ CH 12+160.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Fouling point</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00165-00</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>CH 10+425.000 ~ CH 12+160.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>CH 00+087</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Ballast Mats(future Line)</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>00+296</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>MFBW</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>CH 00+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Turnout 1st Tamping</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Turnout 2nd Tamping</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Turnout 3rd Tamping</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Turnout Final Tamping</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>-CH 00+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Turnout De-stressing</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>CH 52+426</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>De-streesing Of Rail</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>1sttamping</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>2nd Tamping</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>3rd Tamping</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Final Tamping</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Ballast Profilling</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Control Point</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>4 CONTROL POINT</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Fujairah Clearance And Fouling Marker</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00164-00</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00130</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>未匹配到对应code</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Ballast Mat</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>未匹配到对应code</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>ballast mat</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>FPJ 01A</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>1st_tamping</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>1st_Tamping</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>2nd_tamping</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>2nd_Tamping</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Fin_tamping</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>Fin_Tamping</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>CH 01+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>CH 00+250</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>CH 00+000</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>CH 01+100</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00250</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>CODE-3</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>CH 00+250</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Existing Track Ramoval</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>CH 02+785</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Existing Track Ramoval</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>CH 02+266</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>CODE-3</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>CH 28+414</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>CH 28+425</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>CH 29+500</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G444"/>
+  <autoFilter ref="A1:G378"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$444</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12363,8 +12363,2022 @@
       </c>
       <c r="G378" t="inlineStr"/>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Buffer Stop</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00162-00</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Buffer Stop</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00163-00</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>12+130</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Existing track removal (JBL</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00029-00</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Existing track removal (JBL</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00030-00</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Existing track removal (JBL</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00031-00</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>04+250 ~ 04+331.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SURVEY WORK</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00155-00</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Qty:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SURVEY WORK</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00151-00</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Qty:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Structure gauge inspection</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00158-00</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>11+521 ~ 12+160</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Structure gauge inspection</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00160-00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00144-00</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00145-00</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00146-00</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00147-00</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>DTS 1st</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00148-00</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00149-00</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00150-00</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00152-00</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00153-00</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>DTS 2nd</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00154-00</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Fouling point</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00166-00</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>CH 10+425.000 ~ CH 12+160.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Fouling point</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00165-00</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>CH 10+425.000 ~ CH 12+160.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00004-00</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00005-00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>CH 00+087</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Ballast Mats(future Line)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00157-00</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>00+296</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00006-00</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00008-00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>CH 00+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Turnout 1st Tamping</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00009-00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Turnout 2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00010-00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Turnout 3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00011-00</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Turnout Final Tamping</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00012-00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-CH 00+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00013-00</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Turnout De-stressing</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00014-00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>CH 52+426</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>De-streesing Of Rail</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00015-00</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>1sttamping</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00016-00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00017-00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00018-00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00019-00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>4 CONTROL POINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Fujairah Clearance And Fouling Marker</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00164-00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Structural Gauge</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00168-00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Track Maker</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00170-00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Buffer Stop</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00130</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>HJR19A</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>HJR19B</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>CH 50+942</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Fujairah Loop</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ballast Mat</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>FPJ 01A</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1st_tamping</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>1st_Tamping</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2nd_tamping</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>2nd_Tamping</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Fin_tamping</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00243</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>CH 01+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00251</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>CH 00+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00253</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>CH 00+000</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00244</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>CH 01+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00250</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>CH 00+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00245</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>CH 02+785</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00254</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>CH 02+266</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00247</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00360</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>CH 28+414</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>CH 28+425</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>CH 29+500</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G378"/>
+  <autoFilter ref="A1:G444"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -13636,7 +13636,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CH 12+799 ~ CH 12+867</t>
+          <t>CH 12+813 ~ CH 12+867</t>
         </is>
       </c>
     </row>
@@ -559,19 +559,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-02747-01</t>
+          <t>P2225-PS4-GQC-IR-03016-00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3016</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CH 01+825 ~ CH 04+500</t>
+          <t>CH 00+600 ~ CH 01+786</t>
         </is>
       </c>
     </row>
@@ -588,7 +592,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03016-00</t>
+          <t>P2225-PS4-GQC-IR-03440-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -596,15 +600,11 @@
           <t>CODE-2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CH 00+600 ~ CH 01+786</t>
+          <t>CH 01+786 ~ CH 01+825</t>
         </is>
       </c>
     </row>
@@ -621,23 +621,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03042-00</t>
+          <t>P2225-PS4-GQC-IR-02747-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3042</t>
-        </is>
-      </c>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CH 04+500 ~ CH 06+000</t>
+          <t>CH 01+825 ~ CH 04+500</t>
         </is>
       </c>
     </row>
@@ -654,7 +650,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03045-00</t>
+          <t>P2225-PS4-GQC-IR-03042-00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -662,9 +658,17 @@
           <t>CODE-2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CH 04+500 ~ CH 06+000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,19 +683,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03326-01</t>
+          <t>P2225-PS4-GQC-IR-03565-00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CH 06+750 ~ CH 07+725</t>
+          <t>CH 06+000 ~ CH 06+750</t>
         </is>
       </c>
     </row>
@@ -708,23 +712,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03763-00</t>
+          <t>P2225-PS4-GQC-IR-03326-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3763</t>
-        </is>
-      </c>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CH 07+700 ~ CH 08+680</t>
+          <t>CH 06+750 ~ CH 07+725</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03327-00</t>
+          <t>P2225-PS4-GQC-IR-03763-00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -749,9 +749,17 @@
           <t>CODE-2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3763</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CH 07+700 ~ CH 08+680</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -766,7 +774,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03440-01</t>
+          <t>P2225-PS4-GQC-IR-03966-00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -778,7 +786,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CH 01+786 ~ CH 01+825</t>
+          <t>CH 10+560 ~ CH 11+380</t>
         </is>
       </c>
     </row>
@@ -795,7 +803,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03565-00</t>
+          <t>P2225-PS4-GQC-IR-03967-00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -807,7 +815,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CH 06+000 ~ CH 06+750</t>
+          <t>CH 11+380 ~ CH 12+350</t>
         </is>
       </c>
     </row>
@@ -824,17 +832,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03851-00</t>
+          <t>P2225-PS4-GQC-IR-04109-00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bottom ballast</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CH 12+350 ~ CH 13+160</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -849,7 +869,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03742-00</t>
+          <t>P2225-PS4-GQC-IR-03968-00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -859,7 +879,11 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CH 13+160 ~ CH 14+360</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -874,17 +898,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03970-00</t>
+          <t>P2225-PS4-GQC-IR-04165-00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bottom ballast</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CH 14+360 ~ CH 14+900</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,7 +935,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03966-00</t>
+          <t>P2225-PS4-GQC-IR-03045-00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -909,11 +945,7 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CH 10+560 ~ CH 11+380</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,7 +960,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03967-00</t>
+          <t>P2225-PS4-GQC-IR-03851-00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -938,11 +970,7 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CH 11+380 ~ CH 12+350</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,7 +985,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03968-00</t>
+          <t>P2225-PS4-GQC-IR-03327-00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -967,11 +995,7 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CH 13+160 ~ CH 14+360</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,7 +1010,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03969-00</t>
+          <t>P2225-PS4-GQC-IR-03742-00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1011,29 +1035,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-04109-00</t>
+          <t>P2225-PS4-GQC-IR-03970-00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bottom ballast</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CH 12+350 ~ CH 13+160</t>
-        </is>
-      </c>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1048,24 +1060,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-04164-00</t>
+          <t>P2225-PS4-GQC-IR-03969-00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Bottom ballast</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1081,7 +1085,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-04166-00</t>
+          <t>P2225-PS4-GQC-IR-04164-00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1114,7 +1118,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-04165-00</t>
+          <t>P2225-PS4-GQC-IR-04166-00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1132,11 +1136,7 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CH 14+360 ~ CH 14+900</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-02748-01</t>
+          <t>P2225-PS4-GQC-IR-03017-00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CH 01+825 ~ CH 04+500</t>
+          <t>CH 00+600 ~ CH 01+786</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03017-00</t>
+          <t>P2225-PS4-GQC-IR-03441-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1200,7 +1200,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CH 00+600 ~ CH 01+786</t>
+          <t>CH 01+786 ~ CH 01+825</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03046-01</t>
+          <t>P2225-PS4-GQC-IR-02748-01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1231,7 +1231,11 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CH 01+825 ~ CH 04+500</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03764-00</t>
+          <t>P2225-PS4-GQC-IR-03043-00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1260,7 +1264,11 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CH 04+500 ~ CH 06+000</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1275,7 +1283,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03043-00</t>
+          <t>P2225-PS4-GQC-IR-03566-00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1291,7 +1299,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CH 04+500 ~ CH 06+000</t>
+          <t>CH 06+000 ~ CH 06+750</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1316,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03324-01</t>
+          <t>P2225-PS4-GQC-IR-03325-01</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1322,7 +1330,11 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CH 06+750 ~ CH 07+725</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1337,12 +1349,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03325-01</t>
+          <t>P2225-PS4-GQC-IR-03461-01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1353,7 +1365,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CH 06+750 ~ CH 07+725</t>
+          <t>CH 07+725 ~ CH 08+690</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1382,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03441-01</t>
+          <t>P2225-PS4-GQC-IR-03971-00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1386,7 +1398,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CH 01+786 ~ CH 01+825</t>
+          <t>CH 11+380 ~ CH 12+500</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1415,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03463-01</t>
+          <t>P2225-PS4-GQC-IR-04113-00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1416,8 +1428,16 @@
           <t>Track laying</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CH 12+500 ~ CH 13+325</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1432,7 +1452,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03566-00</t>
+          <t>P2225-PS4-GQC-IR-03046-01</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1446,11 +1466,7 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>CH 06+000 ~ CH 06+750</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1465,7 +1481,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03461-01</t>
+          <t>P2225-PS4-GQC-IR-03764-00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1479,11 +1495,7 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>CH 07+725 ~ CH 08+690</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1498,7 +1510,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03765-00</t>
+          <t>P2225-PS4-GQC-IR-03324-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1527,7 +1539,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03743-00</t>
+          <t>P2225-PS4-GQC-IR-03463-01</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1556,7 +1568,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03848-00</t>
+          <t>P2225-PS4-GQC-IR-03765-00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1585,7 +1597,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03849-00</t>
+          <t>P2225-PS4-GQC-IR-03743-00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1614,7 +1626,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03971-00</t>
+          <t>P2225-PS4-GQC-IR-03848-00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1628,11 +1640,7 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>CH 11+380 ~ CH 12+500</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1647,7 +1655,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03972-00</t>
+          <t>P2225-PS4-GQC-IR-03849-00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1676,12 +1684,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-04113-00</t>
+          <t>P2225-PS4-GQC-IR-03972-00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1689,16 +1697,8 @@
           <t>Track laying</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>CH 12+500 ~ CH 13+325</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-02746-01</t>
+          <t>P2225-PS4-GQC-IR-03015-01</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CH 01+825 ~ CH 04+483</t>
+          <t>CH 00+600 ~ CH 01+763</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03041-01</t>
+          <t>P2225-PS4-GQC-IR-02746-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CH 04+483 ~ CH 05+808</t>
+          <t>CH 01+825 ~ CH 04+483</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03044-01</t>
+          <t>P2225-PS4-GQC-IR-03041-01</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1871,7 +1871,11 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CH 04+483 ~ CH 05+808</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1886,7 +1890,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03787-00</t>
+          <t>P2225-PS4-GQC-IR-03567-00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1904,7 +1908,11 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CH 05+980 ~ CH 06+685</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1919,7 +1927,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03015-01</t>
+          <t>P2225-PS4-GQC-IR-03208-01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1939,7 +1947,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CH 00+600 ~ CH 01+763</t>
+          <t>CH 06+700 ~ CH 07+725</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1964,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03208-01</t>
+          <t>P2225-PS4-GQC-IR-03321-01</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1976,7 +1984,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CH 06+700 ~ CH 07+725</t>
+          <t>CH 07+730 ~ CH 08+680</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2001,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03321-01</t>
+          <t>P2225-PS4-GQC-IR-03668-00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2013,7 +2021,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CH 07+730 ~ CH 08+680</t>
+          <t>CH 10+975 ~ CH 11+500</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2038,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03322-01</t>
+          <t>P2225-PS4-GQC-IR-03669-00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2048,7 +2056,11 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+300</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2063,7 +2075,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03323-01</t>
+          <t>P2225-PS4-GQC-IR-04110-00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2081,7 +2093,11 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CH 12+350 ~ CH 13+100</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2096,7 +2112,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03567-00</t>
+          <t>P2225-PS4-GQC-IR-03875-00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2116,7 +2132,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CH 05+980 ~ CH 06+685</t>
+          <t>CH 13+120 ~ CH 14+900</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2149,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03568-00</t>
+          <t>P2216-S04-GQC-IR-03044-01</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2166,7 +2182,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03670-00</t>
+          <t>P2216-S04-GQC-IR-03787-00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2199,7 +2215,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03668-00</t>
+          <t>P2225-PS4-GQC-IR-03322-01</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2217,11 +2233,7 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>CH 10+975 ~ CH 11+500</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2236,12 +2248,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03669-00</t>
+          <t>P2225-PS4-GQC-IR-03323-01</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2254,11 +2266,7 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+300</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2273,7 +2281,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03850-00</t>
+          <t>P2225-PS4-GQC-IR-03568-00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2306,7 +2314,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03875-00</t>
+          <t>P2225-PS4-GQC-IR-03670-00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2324,11 +2332,7 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>CH 13+120 ~ CH 14+900</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2347,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-03878-00</t>
+          <t>P2225-PS4-GQC-IR-03850-00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2376,12 +2380,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>P2225-PS4-GQC-IR-04110-00</t>
+          <t>P2225-PS4-GQC-IR-03878-00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2394,11 +2398,7 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>CH 12+350 ~ CH 13+100</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2739,7 +2739,11 @@
           <t>BOTTOM BALLAST</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>WESTERN CHORD</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>CH 01+400 ~ CH 02+468</t>
@@ -7214,7 +7218,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7243,7 +7247,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7276,7 +7280,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7309,7 +7313,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -7342,7 +7346,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -7371,7 +7375,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -7400,7 +7404,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -14190,24 +14190,24 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00250</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
-          <t>CH 00+250</t>
+          <t>CH 02+785</t>
         </is>
       </c>
     </row>
@@ -14224,19 +14224,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
-          <t>CH 02+785</t>
+          <t>CH 02+266</t>
         </is>
       </c>
     </row>
@@ -14248,24 +14248,28 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>GMC</t>
+        </is>
+      </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>CH 02+266</t>
+          <t>/</t>
         </is>
       </c>
     </row>
@@ -14282,17 +14286,25 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>SHA</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -12944,14 +12944,18 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>CH 10+425.000 ~ CH 12+160.000</t>
+          <t>CH 11+521.000 ~ CH 12+160.000</t>
         </is>
       </c>
     </row>
@@ -12977,10 +12981,14 @@
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>CH 10+425.000 ~ CH 12+160.000</t>
+          <t>CH 10+425.000 ~ CH 11+521.000</t>
         </is>
       </c>
     </row>
@@ -13709,12 +13717,12 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$445</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13013,11 +13013,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13042,11 +13046,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
-          <t>CH 00+087</t>
+          <t>CH 00+087.000 ~ CH 00+158.000</t>
         </is>
       </c>
     </row>
@@ -13071,11 +13079,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Ballast MATS(future line)</t>
+        </is>
+      </c>
       <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
-          <t>00+296</t>
+          <t>CH 00+296.000 ~ CH 00+695.000</t>
         </is>
       </c>
     </row>
@@ -13100,11 +13112,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+043.000</t>
         </is>
       </c>
     </row>
@@ -13129,11 +13145,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>MFBW</t>
+        </is>
+      </c>
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
-          <t>CH 00+043</t>
+          <t>CH 00+043.000 ~ CH 00+703.000</t>
         </is>
       </c>
     </row>
@@ -13158,11 +13178,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Turnout 1st tamping</t>
+        </is>
+      </c>
       <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
-          <t>CH 00+100</t>
+          <t>CH 00+100.000 ~ CH 00+143.000</t>
         </is>
       </c>
     </row>
@@ -13187,11 +13211,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Turnout 2nd tamping</t>
+        </is>
+      </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
-          <t>CH 00+100</t>
+          <t>CH 00+100.000 ~ CH 00+143.000</t>
         </is>
       </c>
     </row>
@@ -13216,11 +13244,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Turnout 3rd tamping</t>
+        </is>
+      </c>
       <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
-          <t>CH 00+100</t>
+          <t>CH 00+100.000 ~ CH 00+143.000</t>
         </is>
       </c>
     </row>
@@ -13245,11 +13277,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Turnout Final Tamping</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
-          <t>-CH 00+100</t>
+          <t>CH 52+476.000 ~ CH 52+719.000</t>
         </is>
       </c>
     </row>
@@ -13274,11 +13310,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+043.000</t>
         </is>
       </c>
     </row>
@@ -13303,11 +13343,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Turnout de-stressing</t>
+        </is>
+      </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
-          <t>CH 52+426</t>
+          <t>CH 52+426.000 ~ CH 52+769.000</t>
         </is>
       </c>
     </row>
@@ -13332,11 +13376,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>De-streesing of Rail</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13361,11 +13409,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>1stTamping</t>
+        </is>
+      </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13390,11 +13442,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13419,11 +13475,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13448,11 +13508,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13469,7 +13533,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00000-20</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -13477,11 +13541,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+702.600</t>
         </is>
       </c>
     </row>
@@ -13506,11 +13574,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
-          <t>4 CONTROL POINT</t>
+          <t>4 Control point</t>
         </is>
       </c>
     </row>
@@ -13535,11 +13607,16 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Fujairah clearance 
+and fouling marker</t>
+        </is>
+      </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/ ~ /</t>
         </is>
       </c>
     </row>
@@ -13564,11 +13641,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Structural gauge</t>
+        </is>
+      </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+000.000 ~ CH 00+703.000</t>
         </is>
       </c>
     </row>
@@ -13593,11 +13674,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Track maker</t>
+        </is>
+      </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/ ~ /</t>
         </is>
       </c>
     </row>
@@ -13609,61 +13694,61 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00130</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr"/>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Track maker</t>
+        </is>
+      </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/ ~ /</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>/ ~ /</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13765,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -13695,12 +13780,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>HJR19B</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CH 50+942</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
@@ -13712,32 +13797,32 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
@@ -13749,22 +13834,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -13774,24 +13859,24 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 50+200</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -13801,17 +13886,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13908,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -13838,17 +13923,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13945,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -13875,7 +13960,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -13922,7 +14007,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
@@ -13934,7 +14019,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -13949,7 +14034,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -13971,7 +14056,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -13986,7 +14071,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -13996,7 +14081,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14093,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -14023,7 +14108,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -14045,7 +14130,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -14060,7 +14145,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -14077,29 +14162,37 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -14116,7 +14209,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -14124,11 +14217,15 @@
           <t>CODE-2</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr"/>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
-          <t>CH 00+250</t>
+          <t>CH 01+100.000 ~ CH 02+416.371</t>
         </is>
       </c>
     </row>
@@ -14145,19 +14242,23 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr"/>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
-          <t>CH 00+000</t>
+          <t>CH 00+250.000 ~ CH 01+100.000</t>
         </is>
       </c>
     </row>
@@ -14169,24 +14270,28 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
-          <t>CH 01+100</t>
+          <t>CH 00+000.000 ~ CH 00+250.000</t>
         </is>
       </c>
     </row>
@@ -14198,12 +14303,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -14211,11 +14316,15 @@
           <t>CODE-2</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr"/>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
-          <t>CH 02+785</t>
+          <t>CH 01+100.000 ~ CH 02+416.371</t>
         </is>
       </c>
     </row>
@@ -14232,19 +14341,23 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr"/>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
-          <t>CH 02+266</t>
+          <t>CH 02+785.000 ~ CH 02+867.000</t>
         </is>
       </c>
     </row>
@@ -14256,28 +14369,28 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-3</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>GMC</t>
-        </is>
-      </c>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>CH 02+266.000 ~ CH 02+331.000</t>
         </is>
       </c>
     </row>
@@ -14294,52 +14407,56 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>SHA</t>
-        </is>
-      </c>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/ ~ /</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
-          <t>CH 28+414</t>
+          <t>/ ~ /</t>
         </is>
       </c>
     </row>
@@ -14351,24 +14468,28 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr"/>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
-          <t>CH 28+425</t>
+          <t>CH 28+414.000 ~ CH 31+078.303</t>
         </is>
       </c>
     </row>
@@ -14385,24 +14506,61 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr"/>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
-          <t>CH 29+500</t>
+          <t>CH 28+425.000 ~ CH 29+500.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>CH 29+500.000 ~ CH 31+078.303</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G444"/>
+  <autoFilter ref="A1:G445"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$445</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$446</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G445"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9037,11 +9037,7 @@
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>CH 08+252.000 ~ CH 08+860.000</t>
-        </is>
-      </c>
+      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9066,7 +9062,11 @@
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>CH 00+386.000 ~ CH 08+912.000</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9091,11 +9091,7 @@
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 08+912.000</t>
-        </is>
-      </c>
+      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9124,11 +9120,7 @@
           <t>western chord</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>CH 00+424.000 ~ CH 02+468.000</t>
-        </is>
-      </c>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9155,7 +9147,7 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>CH 01+693.000 ~ CH 01+935.000</t>
+          <t>CH 02+620.000 ~ CH 07+660.000</t>
         </is>
       </c>
     </row>
@@ -9458,11 +9450,7 @@
           <t>JBL track1</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 08+000.000</t>
-        </is>
-      </c>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9491,11 +9479,7 @@
           <t>JBL track1</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>CH 08+000.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9524,7 +9508,11 @@
           <t>Dubai station</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9553,11 +9541,7 @@
           <t>Dubai station</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>CH 11+521.000 ~ CH 12+155.090</t>
-        </is>
-      </c>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9586,11 +9570,7 @@
           <t>JBL track1</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>CH 10+720.000 ~ CH 11+521.000</t>
-        </is>
-      </c>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9619,7 +9599,11 @@
           <t>JBL track2</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9648,11 +9632,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 08+000.000</t>
-        </is>
-      </c>
+      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9681,11 +9661,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>CH 08+000.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9714,11 +9690,7 @@
           <t>Dubai station</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>CH 11+521.000 ~ CH 12+155.097</t>
-        </is>
-      </c>
+      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9747,7 +9719,11 @@
           <t>Dubai station</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9776,7 +9752,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9805,11 +9785,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>CH 10+100.000 ~ CH 11+521.000</t>
-        </is>
-      </c>
+      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10718,7 +10694,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>CH 09+532 ~ CH 09+875</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10747,7 +10727,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>CH 10+570 ~ CH 10+913</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10776,11 +10760,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>CH 04+250 ~ CH 05+500</t>
-        </is>
-      </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10809,11 +10789,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>CH 05+500 ~ CH 06+696</t>
-        </is>
-      </c>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10842,11 +10818,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>CH 06+696 ~ CH 07+900</t>
-        </is>
-      </c>
+      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10875,11 +10847,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>CH 07+900 ~ CH 08+916</t>
-        </is>
-      </c>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10908,11 +10876,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>CH 11+521 ~ CH 12+155</t>
-        </is>
-      </c>
+      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10941,7 +10905,11 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10970,11 +10938,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>CH 10+935 ~ CH 11+521</t>
-        </is>
-      </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11003,7 +10967,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>CH 10+998 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11032,7 +11000,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>CH 10+720 ~ CH 10+998</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11061,11 +11033,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>CH 04+100 ~ CH 04+333</t>
-        </is>
-      </c>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11094,11 +11062,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>CH 08+916 ~ CH 09+675</t>
-        </is>
-      </c>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11127,11 +11091,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>CH 09+675 ~ CH 10+935</t>
-        </is>
-      </c>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12601,11 +12561,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>11+521 ~ 12+160</t>
-        </is>
-      </c>
+      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -12634,7 +12590,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>CH 04+425.000 ~ CH 11+521.000</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12953,11 +12913,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>CH 11+521.000 ~ CH 12+160.000</t>
-        </is>
-      </c>
+      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -12986,11 +12942,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>CH 10+425.000 ~ CH 11+521.000</t>
-        </is>
-      </c>
+      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13019,11 +12971,7 @@
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -13052,11 +13000,7 @@
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>CH 00+087.000 ~ CH 00+158.000</t>
-        </is>
-      </c>
+      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13085,11 +13029,7 @@
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>CH 00+296.000 ~ CH 00+695.000</t>
-        </is>
-      </c>
+      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -13118,11 +13058,7 @@
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+043.000</t>
-        </is>
-      </c>
+      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13151,11 +13087,7 @@
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>CH 00+043.000 ~ CH 00+703.000</t>
-        </is>
-      </c>
+      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -13184,11 +13116,7 @@
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>CH 00+100.000 ~ CH 00+143.000</t>
-        </is>
-      </c>
+      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -13217,11 +13145,7 @@
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>CH 00+100.000 ~ CH 00+143.000</t>
-        </is>
-      </c>
+      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -13250,11 +13174,7 @@
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>CH 00+100.000 ~ CH 00+143.000</t>
-        </is>
-      </c>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -13283,11 +13203,7 @@
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>CH 52+476.000 ~ CH 52+719.000</t>
-        </is>
-      </c>
+      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13316,11 +13232,7 @@
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+043.000</t>
-        </is>
-      </c>
+      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -13349,11 +13261,7 @@
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>CH 52+426.000 ~ CH 52+769.000</t>
-        </is>
-      </c>
+      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -13382,11 +13290,7 @@
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -13415,11 +13319,7 @@
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -13448,11 +13348,7 @@
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -13481,11 +13377,7 @@
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -13514,11 +13406,7 @@
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -13547,11 +13435,7 @@
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+702.600</t>
-        </is>
-      </c>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -13580,11 +13464,7 @@
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>4 Control point</t>
-        </is>
-      </c>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -13614,11 +13494,7 @@
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>/ ~ /</t>
-        </is>
-      </c>
+      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -13647,11 +13523,7 @@
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+703.000</t>
-        </is>
-      </c>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -13680,11 +13552,7 @@
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>/ ~ /</t>
-        </is>
-      </c>
+      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -13694,7 +13562,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Track Maker</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -13704,20 +13572,16 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Track maker</t>
+          <t>Existing track removal</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>/ ~ /</t>
-        </is>
-      </c>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -13746,11 +13610,7 @@
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>/ ~ /</t>
-        </is>
-      </c>
+      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -13903,17 +13763,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -13923,17 +13783,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13805,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -13960,17 +13820,17 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13842,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -13997,7 +13857,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -14044,7 +13904,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
@@ -14056,7 +13916,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -14071,7 +13931,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -14093,7 +13953,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -14108,7 +13968,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -14118,7 +13978,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -14130,7 +13990,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -14145,7 +14005,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -14167,7 +14027,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -14182,7 +14042,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -14199,33 +14059,37 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>CH 01+100.000 ~ CH 02+416.371</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14106,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14256,11 +14120,7 @@
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>CH 00+250.000 ~ CH 01+100.000</t>
-        </is>
-      </c>
+      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -14275,12 +14135,12 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -14289,11 +14149,7 @@
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>CH 00+000.000 ~ CH 00+250.000</t>
-        </is>
-      </c>
+      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -14303,30 +14159,26 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>CH 01+100.000 ~ CH 02+416.371</t>
-        </is>
-      </c>
+      <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -14336,12 +14188,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -14351,15 +14203,11 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>CH 02+785.000 ~ CH 02+867.000</t>
-        </is>
-      </c>
+      <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -14374,12 +14222,12 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -14388,11 +14236,7 @@
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>CH 02+266.000 ~ CH 02+331.000</t>
-        </is>
-      </c>
+      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -14402,30 +14246,26 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>existing track ramoval</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>/ ~ /</t>
-        </is>
-      </c>
+      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -14440,12 +14280,12 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-3</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -14454,44 +14294,36 @@
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>/ ~ /</t>
-        </is>
-      </c>
+      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>CH 28+414.000 ~ CH 31+078.303</t>
-        </is>
-      </c>
+      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -14501,30 +14333,26 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>CH 28+425.000 ~ CH 29+500.000</t>
-        </is>
-      </c>
+      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -14539,28 +14367,53 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
           <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
+      <c r="D446" t="inlineStr">
         <is>
           <t>UR</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr">
+      <c r="E446" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>CH 29+500.000 ~ CH 31+078.303</t>
-        </is>
-      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G445"/>
+  <autoFilter ref="A1:G446"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -9057,7 +9057,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ballast Mats(future Line)</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Ballast MATS(future line)</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -13572,7 +13572,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$464</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9130,26 +9130,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Datum plate</t>
+          <t>Fouling marker &amp;clearance point（MBZ)</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07096-00</t>
+          <t>P2216-S04-GQC-IR-07068-00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>CH 02+620.000 ~ CH 07+660.000</t>
-        </is>
-      </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9159,17 +9155,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Datum plate</t>
+          <t>Fouling marker &amp;clearance point（MBZ)</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07546-00</t>
+          <t>P2216-S04-GQC-IR-07067-00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -9183,87 +9179,75 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>Datum plate</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00025-00</t>
+          <t>P2216-S04-GQC-IR-07096-00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>JBL TRACK 1</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>CH 02+620.000 ~ CH 07+660.000</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>Datum plate</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00075-00</t>
+          <t>P2216-S04-GQC-IR-07546-00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>JBL TRACK 2</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>CH 11+181.990 ~ CH 11+525.370</t>
-        </is>
-      </c>
+          <t>western chord</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00023-00</t>
+          <t>P2216-PMB-GQC-IR-07050-00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -9271,102 +9255,86 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CH 11+525.370 ~ CH 11+601.760</t>
+          <t>CH 00+082 ~ CH 03+296</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00076-00</t>
+          <t>P2216-PMB-GQC-IR-07051-00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>JBL TRACK 1</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>CH 03+296 ~ CH 05+070</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00077-00</t>
+          <t>P2216-PMB-GQC-IR-07052-00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>CH 05+070 ~ CH 08+912</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00024-00</t>
+          <t>P2216-PMB-GQC-IR-07053-00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -9374,127 +9342,107 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr"/>
+          <t>western chord</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>CH 00+507 ~ CH 02+403</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00093-00</t>
+          <t>P2216-PMB-GQC-IR-07054-00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>CH 11+887.190 ~ CH 11+979.540</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00051-00</t>
+          <t>P2216-PMB-GQC-IR-07055-00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>JBL track1</t>
-        </is>
-      </c>
+      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>DTS 1st（MBZ)</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00064-00</t>
+          <t>P2216-PMB-GQC-IR-07056-00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>JBL track1</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00068-00</t>
+          <t>P2216-PMB-GQC-IR-07057-00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -9503,122 +9451,118 @@
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Dubai station</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
+          <t>CH 00+082 ~ CH 03+296</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00069-00</t>
+          <t>P2216-PMB-GQC-IR-07058-00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Dubai station</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>CH 03+296 ~ CH 05+070</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00109-00</t>
+          <t>P2216-PMB-GQC-IR-07059-00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>JBL track1</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>CH 05+070 ~ CH 08+912</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00108-00</t>
+          <t>P2216-PMB-GQC-IR-07060-00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>JBL track2</t>
+          <t>western chord</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 00+507 ~ CH 02+403</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00050-00</t>
+          <t>P2216-PMB-GQC-IR-07061-00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -9627,69 +9571,57 @@
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00059-00</t>
+          <t>P2216-PMB-GQC-IR-07062-00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>DTS 2nd（MBZ)</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00066-00</t>
+          <t>P2216-PMB-GQC-IR-07063-00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Dubai station</t>
-        </is>
-      </c>
+      <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -9700,30 +9632,30 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00067-00</t>
+          <t>P2216-S04-GQC-IR-00025-00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Dubai station</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+          <t>JBL TRACK 1</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9733,12 +9665,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00094-00</t>
+          <t>P2216-S04-GQC-IR-00075-00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9746,15 +9678,19 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>JBL TRACK 2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 11+181.990 ~ CH 11+525.370</t>
         </is>
       </c>
     </row>
@@ -9766,12 +9702,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00107-00</t>
+          <t>P2216-S04-GQC-IR-00023-00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9779,13 +9715,21 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr"/>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>CH 11+525.370 ~ CH 11+601.760</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9795,30 +9739,30 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00065-00</t>
+          <t>P2216-S04-GQC-IR-00076-00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr"/>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>CH 04+340 ~ CH 05+415</t>
-        </is>
-      </c>
+          <t>JBL TRACK 1</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9828,12 +9772,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00070-00</t>
+          <t>P2216-S04-GQC-IR-00077-00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9841,17 +9785,17 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>CH 05+415 ~ CH 06+630</t>
-        </is>
-      </c>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9861,30 +9805,30 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00072-00</t>
+          <t>P2216-S04-GQC-IR-00024-00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>CH 06+630 ~ CH 08+504</t>
-        </is>
-      </c>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9894,12 +9838,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00073-00</t>
+          <t>P2216-S04-GQC-IR-00093-00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9907,15 +9851,19 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO STATION</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>CH 08+504 ~ CH 09+630</t>
+          <t>CH 11+887.190 ~ CH 11+979.540</t>
         </is>
       </c>
     </row>
@@ -9927,30 +9875,26 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00074-00</t>
+          <t>P2216-S04-GQC-IR-00051-00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>CH 09+700 ~ CH 10+640</t>
-        </is>
-      </c>
+          <t>JBL track1</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9960,30 +9904,26 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00099-00</t>
+          <t>P2216-S04-GQC-IR-00064-00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>CH 10+640 ~ CH 11+521</t>
-        </is>
-      </c>
+          <t>JBL track1</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9993,28 +9933,28 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00100-00</t>
+          <t>P2216-S04-GQC-IR-00068-00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CH 11+521 ~ CH 12+155</t>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
         </is>
       </c>
     </row>
@@ -10026,12 +9966,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00101-00</t>
+          <t>P2216-S04-GQC-IR-00069-00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -10042,7 +9982,7 @@
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
@@ -10055,23 +9995,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00102-00</t>
+          <t>P2216-S04-GQC-IR-00109-00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL track1</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -10084,26 +10024,30 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00156-00</t>
+          <t>P2216-S04-GQC-IR-00108-00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr"/>
+          <t>JBL track2</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10113,12 +10057,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00027-00</t>
+          <t>P2216-S04-GQC-IR-00050-00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -10142,12 +10086,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00038-00</t>
+          <t>P2216-S04-GQC-IR-00059-00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -10161,11 +10105,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
-        </is>
-      </c>
+      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10175,12 +10115,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00042-00</t>
+          <t>P2216-S04-GQC-IR-00066-00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -10191,7 +10131,7 @@
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
@@ -10204,12 +10144,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00056-00</t>
+          <t>P2216-S04-GQC-IR-00067-00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -10220,12 +10160,12 @@
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
         </is>
       </c>
     </row>
@@ -10237,12 +10177,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00078-00</t>
+          <t>P2216-S04-GQC-IR-00094-00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -10258,7 +10198,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
         </is>
       </c>
     </row>
@@ -10270,17 +10210,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00081-00</t>
+          <t>P2216-S04-GQC-IR-00107-00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -10289,11 +10229,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
-        </is>
-      </c>
+      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10303,28 +10239,28 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00084-00</t>
+          <t>P2216-S04-GQC-IR-00065-00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
+          <t>CH 04+340 ~ CH 05+415</t>
         </is>
       </c>
     </row>
@@ -10336,12 +10272,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00087-00</t>
+          <t>P2216-S04-GQC-IR-00070-00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -10355,7 +10291,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>CH 05+415 ~ CH 06+630</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10365,26 +10305,30 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00090-00</t>
+          <t>P2216-S04-GQC-IR-00072-00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>CH 06+630 ~ CH 08+504</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10394,17 +10338,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00035-00</t>
+          <t>P2216-S04-GQC-IR-00073-00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
@@ -10413,7 +10357,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>CH 08+504 ~ CH 09+630</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10423,12 +10371,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00039-00</t>
+          <t>P2216-S04-GQC-IR-00074-00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -10444,7 +10392,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
+          <t>CH 09+700 ~ CH 10+640</t>
         </is>
       </c>
     </row>
@@ -10456,17 +10404,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00043-00</t>
+          <t>P2216-S04-GQC-IR-00099-00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -10475,7 +10423,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>CH 10+640 ~ CH 11+521</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10485,12 +10437,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00055-00</t>
+          <t>P2216-S04-GQC-IR-00100-00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -10501,12 +10453,12 @@
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
+          <t>CH 11+521 ~ CH 12+155</t>
         </is>
       </c>
     </row>
@@ -10518,17 +10470,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00079-00</t>
+          <t>P2216-S04-GQC-IR-00101-00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -10537,11 +10489,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10551,30 +10499,26 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00082-00</t>
+          <t>P2216-S04-GQC-IR-00102-00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10584,30 +10528,26 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00085-00</t>
+          <t>P2216-S04-GQC-IR-00156-00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10617,17 +10557,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00088-00</t>
+          <t>P2216-S04-GQC-IR-00027-00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -10646,12 +10586,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00091-00</t>
+          <t>P2216-S04-GQC-IR-00038-00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -10662,10 +10602,14 @@
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10675,17 +10619,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00048-00</t>
+          <t>P2216-S04-GQC-IR-00042-00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10694,11 +10638,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>CH 09+532 ~ CH 09+875</t>
-        </is>
-      </c>
+      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10708,17 +10648,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00052-00</t>
+          <t>P2216-S04-GQC-IR-00056-00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -10729,7 +10669,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>CH 10+570 ~ CH 10+913</t>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10681,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00095-00</t>
+          <t>P2216-S04-GQC-IR-00078-00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10760,7 +10700,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10770,17 +10714,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00096-00</t>
+          <t>P2216-S04-GQC-IR-00081-00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -10789,7 +10733,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10799,26 +10747,30 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00097-00</t>
+          <t>P2216-S04-GQC-IR-00084-00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10828,17 +10780,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00122-00</t>
+          <t>P2216-S04-GQC-IR-00087-00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
@@ -10857,12 +10809,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00114-00</t>
+          <t>P2216-S04-GQC-IR-00090-00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10886,12 +10838,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00115-00</t>
+          <t>P2216-S04-GQC-IR-00035-00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10902,14 +10854,10 @@
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10919,17 +10867,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00116-00</t>
+          <t>P2216-S04-GQC-IR-00039-00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
@@ -10938,7 +10886,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10948,17 +10900,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00117-00</t>
+          <t>P2216-S04-GQC-IR-00043-00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
@@ -10967,11 +10919,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>CH 10+998 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10981,17 +10929,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00118-00</t>
+          <t>P2216-S04-GQC-IR-00055-00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -11002,7 +10950,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>CH 10+720 ~ CH 10+998</t>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
         </is>
       </c>
     </row>
@@ -11014,12 +10962,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00123-00</t>
+          <t>P2216-S04-GQC-IR-00079-00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -11033,7 +10981,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11043,12 +10995,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00124-00</t>
+          <t>P2216-S04-GQC-IR-00082-00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -11062,7 +11014,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11072,26 +11028,30 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00125-00</t>
+          <t>P2216-S04-GQC-IR-00085-00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11101,17 +11061,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00033-00</t>
+          <t>P2216-S04-GQC-IR-00088-00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -11120,11 +11080,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11134,23 +11090,23 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00026-00</t>
+          <t>P2216-S04-GQC-IR-00091-00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G338" t="inlineStr"/>
@@ -11163,12 +11119,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00046-00</t>
+          <t>P2216-S04-GQC-IR-00048-00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -11182,7 +11138,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>CH 09+532 ~ CH 09+875</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11192,12 +11152,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00049-00</t>
+          <t>P2216-S04-GQC-IR-00052-00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -11213,7 +11173,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>CH 04+250 ~ CH 04+315</t>
+          <t>CH 10+570 ~ CH 10+913</t>
         </is>
       </c>
     </row>
@@ -11225,12 +11185,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00110-00</t>
+          <t>P2216-S04-GQC-IR-00095-00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11241,7 +11201,7 @@
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G341" t="inlineStr"/>
@@ -11254,12 +11214,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00111-00</t>
+          <t>P2216-S04-GQC-IR-00096-00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -11270,14 +11230,10 @@
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>CH 11+702 ~ CH 11+737</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11287,26 +11243,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00112-00</t>
+          <t>P2216-S04-GQC-IR-00097-00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>CH 10+935 ~ CH 10+989</t>
-        </is>
-      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11316,12 +11272,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00113-00</t>
+          <t>P2216-S04-GQC-IR-00122-00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -11330,7 +11286,11 @@
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -11341,12 +11301,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00047-00</t>
+          <t>P2216-S04-GQC-IR-00114-00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11355,12 +11315,12 @@
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11370,12 +11330,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00034-00</t>
+          <t>P2216-S04-GQC-IR-00115-00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11384,8 +11344,16 @@
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11395,12 +11363,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00053-00</t>
+          <t>P2216-S04-GQC-IR-00116-00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -11409,7 +11377,11 @@
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -11420,12 +11392,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00054-00</t>
+          <t>P2216-S04-GQC-IR-00117-00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -11434,10 +11406,14 @@
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>04+250.00 ~ 04+315.00</t>
+          <t>CH 10+998 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -11449,12 +11425,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00098-00</t>
+          <t>P2216-S04-GQC-IR-00118-00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -11463,8 +11439,16 @@
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>CH 10+720 ~ CH 10+998</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11474,12 +11458,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00119-00</t>
+          <t>P2216-S04-GQC-IR-00123-00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -11488,7 +11472,11 @@
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -11499,12 +11487,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00120-00</t>
+          <t>P2216-S04-GQC-IR-00124-00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11513,7 +11501,11 @@
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -11524,12 +11516,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00121-00</t>
+          <t>P2216-S04-GQC-IR-00125-00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11538,7 +11530,11 @@
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -11549,12 +11545,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00139-00</t>
+          <t>P2216-S04-GQC-IR-00033-00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -11563,8 +11559,16 @@
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11574,12 +11578,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00131-00</t>
+          <t>P2216-S04-GQC-IR-00026-00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -11603,12 +11607,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00132-00</t>
+          <t>P2216-S04-GQC-IR-00046-00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -11632,12 +11636,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00133-00</t>
+          <t>P2216-S04-GQC-IR-00049-00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -11653,7 +11657,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>CH 11+175 ~ CH 11+525</t>
+          <t>CH 04+250 ~ CH 04+315</t>
         </is>
       </c>
     </row>
@@ -11665,12 +11669,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00134-00</t>
+          <t>P2216-S04-GQC-IR-00110-00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11681,7 +11685,7 @@
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G357" t="inlineStr"/>
@@ -11694,12 +11698,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00135-00</t>
+          <t>P2216-S04-GQC-IR-00111-00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -11710,10 +11714,14 @@
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>CH 11+702 ~ CH 11+737</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11723,28 +11731,24 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00136-00</t>
+          <t>P2216-S04-GQC-IR-00112-00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
-          <t>CH 11+525 ~ CH 11+599</t>
+          <t>CH 10+935 ~ CH 10+989</t>
         </is>
       </c>
     </row>
@@ -11756,12 +11760,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00137-00</t>
+          <t>P2216-S04-GQC-IR-00113-00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -11770,11 +11774,7 @@
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00037-00</t>
+          <t>P2216-S04-GQC-IR-00047-00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -11799,12 +11799,12 @@
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00041-00</t>
+          <t>P2216-S04-GQC-IR-00034-00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -11828,16 +11828,8 @@
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>CH 09+480 ~ CH 09+823</t>
-        </is>
-      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -11847,12 +11839,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00045-00</t>
+          <t>P2216-S04-GQC-IR-00053-00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -11861,11 +11853,7 @@
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
@@ -11876,12 +11864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00058-00</t>
+          <t>P2216-S04-GQC-IR-00054-00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -11890,14 +11878,10 @@
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
-          <t>CH 04+100 ~ CH 04+465</t>
+          <t>04+250.00 ~ 04+315.00</t>
         </is>
       </c>
     </row>
@@ -11909,12 +11893,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00063-00</t>
+          <t>P2216-S04-GQC-IR-00098-00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11923,16 +11907,8 @@
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>CH 10+570 ~ CH 10+913</t>
-        </is>
-      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11942,12 +11918,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00103-00</t>
+          <t>P2216-S04-GQC-IR-00119-00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -11956,16 +11932,8 @@
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>CH 04+250 ~ CH 11+521</t>
-        </is>
-      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -11975,12 +11943,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00104-00</t>
+          <t>P2216-S04-GQC-IR-00120-00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -11989,11 +11957,7 @@
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
@@ -12004,12 +11968,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00105-00</t>
+          <t>P2216-S04-GQC-IR-00121-00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -12018,16 +11982,8 @@
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>CH 11+521 ~ CH 12+155</t>
-        </is>
-      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12037,12 +11993,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00106-00</t>
+          <t>P2216-S04-GQC-IR-00139-00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -12051,11 +12007,7 @@
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
@@ -12066,17 +12018,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>REJ</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00138-00</t>
+          <t>P2216-S04-GQC-IR-00131-00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -12095,12 +12047,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00126-00</t>
+          <t>P2216-S04-GQC-IR-00132-00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -12124,12 +12076,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00127-00</t>
+          <t>P2216-S04-GQC-IR-00133-00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -12145,7 +12097,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 11+175 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -12157,12 +12109,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00128-00</t>
+          <t>P2216-S04-GQC-IR-00134-00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -12173,7 +12125,7 @@
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G373" t="inlineStr"/>
@@ -12186,12 +12138,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00129-00</t>
+          <t>P2216-S04-GQC-IR-00135-00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -12202,14 +12154,10 @@
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12219,26 +12167,30 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00140-00</t>
+          <t>P2216-S04-GQC-IR-00136-00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 11+599</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12248,23 +12200,23 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00141-00</t>
+          <t>P2216-S04-GQC-IR-00137-00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G376" t="inlineStr"/>
@@ -12277,23 +12229,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00142-00</t>
+          <t>P2216-S04-GQC-IR-00037-00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G377" t="inlineStr"/>
@@ -12306,26 +12258,30 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00143-00</t>
+          <t>P2216-S04-GQC-IR-00041-00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>CH 09+480 ~ CH 09+823</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12335,21 +12291,25 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00162-00</t>
+          <t>P2216-S04-GQC-IR-00045-00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
@@ -12360,24 +12320,28 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00163-00</t>
+          <t>P2216-S04-GQC-IR-00058-00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>12+130</t>
+          <t>CH 04+100 ~ CH 04+465</t>
         </is>
       </c>
     </row>
@@ -12389,22 +12353,30 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00029-00</t>
+          <t>P2216-S04-GQC-IR-00063-00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>CH 10+570 ~ CH 10+913</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12414,22 +12386,30 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00030-00</t>
+          <t>P2216-S04-GQC-IR-00103-00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>CH 04+250 ~ CH 11+521</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12439,26 +12419,26 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00031-00</t>
+          <t>P2216-S04-GQC-IR-00104-00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>04+250 ~ 04+331.6</t>
-        </is>
-      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12468,12 +12448,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00155-00</t>
+          <t>P2216-S04-GQC-IR-00105-00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -12481,11 +12461,7 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
           <t>EXPO</t>
@@ -12493,7 +12469,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Qty:5</t>
+          <t>CH 11+521 ~ CH 12+155</t>
         </is>
       </c>
     </row>
@@ -12505,12 +12481,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00151-00</t>
+          <t>P2216-S04-GQC-IR-00106-00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -12518,21 +12494,13 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Qty:4</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12542,23 +12510,23 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>REJ</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00158-00</t>
+          <t>P2216-S04-GQC-IR-00138-00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G386" t="inlineStr"/>
@@ -12571,17 +12539,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00160-00</t>
+          <t>P2216-S04-GQC-IR-00126-00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -12590,11 +12558,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>CH 04+425.000 ~ CH 11+521.000</t>
-        </is>
-      </c>
+      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12604,12 +12568,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00144-00</t>
+          <t>P2216-S04-GQC-IR-00127-00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -12618,8 +12582,16 @@
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12629,12 +12601,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00145-00</t>
+          <t>P2216-S04-GQC-IR-00128-00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -12643,7 +12615,11 @@
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
@@ -12654,12 +12630,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00146-00</t>
+          <t>P2216-S04-GQC-IR-00129-00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -12673,7 +12649,11 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -12683,17 +12663,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00147-00</t>
+          <t>P2216-S04-GQC-IR-00140-00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -12702,11 +12682,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -12716,30 +12692,26 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00148-00</t>
+          <t>P2216-S04-GQC-IR-00141-00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12749,21 +12721,25 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00149-00</t>
+          <t>P2216-S04-GQC-IR-00142-00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -12774,21 +12750,25 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00150-00</t>
+          <t>P2216-S04-GQC-IR-00143-00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
@@ -12799,25 +12779,21 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00152-00</t>
+          <t>P2216-S04-GQC-IR-00162-00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -12828,28 +12804,24 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00153-00</t>
+          <t>P2216-S04-GQC-IR-00163-00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
-          <t>CH 10+763 ~ CH 11+525</t>
+          <t>12+130</t>
         </is>
       </c>
     </row>
@@ -12861,30 +12833,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00154-00</t>
+          <t>P2216-S04-GQC-IR-00029-00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -12894,25 +12858,21 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00166-00</t>
+          <t>P2216-S04-GQC-IR-00030-00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -12923,41 +12883,41 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00165-00</t>
+          <t>P2216-S04-GQC-IR-00031-00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>04+250 ~ 04+331.6</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-00155-00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -12967,113 +12927,129 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Qty:5</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-00151-00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Qty:4</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-00166-00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr"/>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-00165-00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Sign markers</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00173-00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -13081,115 +13057,123 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>MFBW</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr"/>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>Sign markers</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00174-00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>Turnout 1st tamping</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Expo</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>CH 11+521.000 ~ CH 12+160.000</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00158-00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>Turnout 2nd tamping</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00160-00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>Turnout 3rd tamping</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>CH 04+425.000 ~ CH 11+521.000</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00144-00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -13197,28 +13181,24 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>Turnout Final Tamping</t>
-        </is>
-      </c>
+      <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00145-00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -13226,28 +13206,24 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>ATW</t>
-        </is>
-      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00146-00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -13255,28 +13231,28 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>Turnout de-stressing</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr"/>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00147-00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -13284,115 +13260,115 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>De-streesing of Rail</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00148-00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>1stTamping</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00149-00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>2nd Tamping</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00150-00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>3rd Tamping</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00152-00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -13400,28 +13376,28 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>Final Tamping</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00000-20</t>
+          <t>P2216-S04-GQC-IR-00153-00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -13429,28 +13405,32 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>Ballast Profilling</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00154-00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -13458,13 +13438,17 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>CONTROL POINT</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -13474,678 +13458,574 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00004-00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00005-00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00157-00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00006-00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00008-00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Turnout 1st Tamping</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00009-00</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Turnout 1st tamping</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Turnout 2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00010-00</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Turnout 2nd tamping</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Turnout 3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00011-00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Turnout 3rd tamping</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Turnout Final Tamping</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00012-00</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Turnout Final Tamping</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00013-00</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Turnout De-stressing</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00014-00</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Turnout de-stressing</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>De-streesing Of Rail</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00015-00</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>De-streesing of Rail</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>1sttamping</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00016-00</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>1stTamping</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00017-00</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00018-00</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00019-00</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00000-20</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C436" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>Track maker</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>Existing track removal</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>buffer stop</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Ballast Mat</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>ballast mat</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>FPJ 01A</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>1st_tamping</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>1st_Tamping</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>2nd_tamping</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>2nd_Tamping</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Fin_tamping</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>Fin_Tamping</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>Structural gauge</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14154,27 +14034,27 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>Track maker</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14183,27 +14063,27 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing track removal</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -14212,27 +14092,27 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>buffer stop</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -14241,17 +14121,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -14261,55 +14141,71 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>HJR19A</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>HJR19B</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>CH 50+942</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14319,101 +14215,711 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Existing Track Removal</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>FPJ 01A</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>1st_tamping</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>1st_Tamping</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2nd_tamping</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>2nd_Tamping</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Fujairah Port</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Fin_tamping</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00243</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00251</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00253</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00244</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00245</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Existing Track Ramoval</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00254</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00247</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>CODE-3</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00256</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
           <t>PL-28</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00360</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
         <is>
           <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr">
+      <c r="D464" t="inlineStr">
         <is>
           <t>UR</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr">
+      <c r="E464" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G446"/>
+  <autoFilter ref="A1:G464"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -9194,7 +9194,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-03044-01</t>
+          <t>P2225-PS4-GQC-IR-03044-01</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-03787-00</t>
+          <t>P2225-PS4-GQC-IR-03787-00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -13497,7 +13497,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>CODE-3</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$464</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$466</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5738,7 +5738,9 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5895,7 +5897,9 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5924,7 +5928,9 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5957,7 +5963,9 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6089,7 +6097,9 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6118,7 +6128,9 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6209,7 +6221,9 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6242,7 +6256,9 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8482,7 +8498,9 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -8635,7 +8653,9 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -8668,7 +8688,9 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -8697,7 +8719,9 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -8722,7 +8746,9 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -8747,7 +8773,9 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -8995,7 +9023,9 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9032,7 +9062,9 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -9130,7 +9162,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Fouling marker &amp;clearance point（MBZ)</t>
+          <t>Fouling marker &amp;clearance point</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9155,7 +9187,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Fouling marker &amp;clearance point（MBZ)</t>
+          <t>Fouling marker &amp;clearance point</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9194,7 +9226,9 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
+Call log:
+  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -9242,7 +9276,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9271,7 +9305,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9300,7 +9334,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9329,7 +9363,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9362,7 +9396,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9387,7 +9421,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9412,7 +9446,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DTS 1st（MBZ)</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9437,7 +9471,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9466,7 +9500,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9495,7 +9529,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9524,7 +9558,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9557,7 +9591,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9582,7 +9616,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9607,7 +9641,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DTS 2nd（MBZ)</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -14762,7 +14796,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -14791,7 +14825,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -14799,7 +14833,11 @@
           <t>Turnout Installation</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
@@ -14828,65 +14866,77 @@
           <t>Turnout Installation</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>SHA01</t>
+        </is>
+      </c>
       <c r="G461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr"/>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr"/>
+          <t>Turnout Destressing</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G463" t="inlineStr"/>
     </row>
     <row r="464">
@@ -14897,29 +14947,87 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr"/>
     </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G464"/>
+  <autoFilter ref="A1:G466"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$466</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$451</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G466"/>
+  <dimension ref="A1:G451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5738,9 +5738,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5897,9 +5895,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5928,9 +5924,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5963,9 +5957,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6097,9 +6089,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6128,9 +6118,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6221,9 +6209,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6256,9 +6242,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8498,9 +8482,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -8653,9 +8635,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -8688,9 +8668,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -8719,9 +8697,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -8746,9 +8722,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -8773,9 +8747,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9023,9 +8995,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9062,9 +9032,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -9162,22 +9130,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Fouling marker &amp;clearance point</t>
+          <t>Datum plate</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07068-00</t>
+          <t>P2216-S04-GQC-IR-07096-00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>CH 02+620.000 ~ CH 07+660.000</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9187,12 +9159,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Fouling marker &amp;clearance point</t>
+          <t>Datum plate</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07067-00</t>
+          <t>P2216-S04-GQC-IR-07546-00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -9211,48 +9183,50 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Datum plate</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07096-00</t>
+          <t>P2216-S04-GQC-IR-00025-00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>网站错误: Page.goto: Timeout 120000ms exceeded.
-Call log:
-  - navigating to "https://npc.rdrive.io/mbz/processes?subcategory-ids=1", waiting until "load"</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>CH 02+620.000 ~ CH 07+660.000</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>JBL TRACK 1</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Datum plate</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07546-00</t>
+          <t>P2216-S04-GQC-IR-00075-00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -9260,28 +9234,36 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>western chord</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr"/>
+          <t>JBL TRACK 2</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>CH 11+181.990 ~ CH 11+525.370</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07050-00</t>
+          <t>P2216-S04-GQC-IR-00023-00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -9289,86 +9271,102 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CH 00+082 ~ CH 03+296</t>
+          <t>CH 11+525.370 ~ CH 11+601.760</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07051-00</t>
+          <t>P2216-S04-GQC-IR-00076-00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>CH 03+296 ~ CH 05+070</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>JBL TRACK 1</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07052-00</t>
+          <t>P2216-S04-GQC-IR-00077-00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>CH 05+070 ~ CH 08+912</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07053-00</t>
+          <t>P2216-S04-GQC-IR-00024-00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -9376,107 +9374,127 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>western chord</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>CH 00+507 ~ CH 02+403</t>
-        </is>
-      </c>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07054-00</t>
+          <t>P2216-S04-GQC-IR-00093-00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>CH 11+887.190 ~ CH 11+979.540</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07055-00</t>
+          <t>P2216-S04-GQC-IR-00051-00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>JBL track1</t>
+        </is>
+      </c>
       <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07056-00</t>
+          <t>P2216-S04-GQC-IR-00064-00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>JBL track1</t>
+        </is>
+      </c>
       <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07057-00</t>
+          <t>P2216-S04-GQC-IR-00068-00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -9485,118 +9503,122 @@
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Dubai station</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>CH 00+082 ~ CH 03+296</t>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07058-00</t>
+          <t>P2216-S04-GQC-IR-00069-00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>CH 03+296 ~ CH 05+070</t>
-        </is>
-      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Dubai station</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07059-00</t>
+          <t>P2216-S04-GQC-IR-00109-00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>CH 05+070 ~ CH 08+912</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>JBL track1</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07060-00</t>
+          <t>P2216-S04-GQC-IR-00108-00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>western chord</t>
+          <t>JBL track2</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CH 00+507 ~ CH 02+403</t>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07061-00</t>
+          <t>P2216-S04-GQC-IR-00050-00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -9605,57 +9627,69 @@
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07062-00</t>
+          <t>P2216-S04-GQC-IR-00059-00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07063-00</t>
+          <t>P2216-S04-GQC-IR-00066-00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Dubai station</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -9666,30 +9700,30 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00025-00</t>
+          <t>P2216-S04-GQC-IR-00067-00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>JBL TRACK 1</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr"/>
+          <t>Dubai station</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9699,12 +9733,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00075-00</t>
+          <t>P2216-S04-GQC-IR-00094-00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9712,19 +9746,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>JBL TRACK 2</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CH 11+181.990 ~ CH 11+525.370</t>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
         </is>
       </c>
     </row>
@@ -9736,12 +9766,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00023-00</t>
+          <t>P2216-S04-GQC-IR-00107-00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9749,21 +9779,13 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>CH 11+525.370 ~ CH 11+601.760</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9773,30 +9795,30 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00076-00</t>
+          <t>P2216-S04-GQC-IR-00065-00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>JBL TRACK 1</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>CH 04+340 ~ CH 05+415</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9806,12 +9828,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00077-00</t>
+          <t>P2216-S04-GQC-IR-00070-00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9819,17 +9841,17 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>CH 05+415 ~ CH 06+630</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9839,30 +9861,30 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00024-00</t>
+          <t>P2216-S04-GQC-IR-00072-00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>CH 06+630 ~ CH 08+504</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9872,12 +9894,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00093-00</t>
+          <t>P2216-S04-GQC-IR-00073-00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9885,19 +9907,15 @@
           <t>CODE-5</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>CH 11+887.190 ~ CH 11+979.540</t>
+          <t>CH 08+504 ~ CH 09+630</t>
         </is>
       </c>
     </row>
@@ -9909,26 +9927,30 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00051-00</t>
+          <t>P2216-S04-GQC-IR-00074-00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JBL track1</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>CH 09+700 ~ CH 10+640</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9938,26 +9960,30 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00064-00</t>
+          <t>P2216-S04-GQC-IR-00099-00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>JBL track1</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>CH 10+640 ~ CH 11+521</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9967,28 +9993,28 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00068-00</t>
+          <t>P2216-S04-GQC-IR-00100-00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
+          <t>CH 11+521 ~ CH 12+155</t>
         </is>
       </c>
     </row>
@@ -10000,12 +10026,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00069-00</t>
+          <t>P2216-S04-GQC-IR-00101-00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -10016,7 +10042,7 @@
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
@@ -10029,23 +10055,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00109-00</t>
+          <t>P2216-S04-GQC-IR-00102-00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>JBL track1</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -10058,30 +10084,26 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00108-00</t>
+          <t>P2216-S04-GQC-IR-00156-00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>JBL track2</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10091,12 +10113,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00050-00</t>
+          <t>P2216-S04-GQC-IR-00027-00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -10120,12 +10142,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00059-00</t>
+          <t>P2216-S04-GQC-IR-00038-00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -10139,7 +10161,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10149,12 +10175,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00066-00</t>
+          <t>P2216-S04-GQC-IR-00042-00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -10165,7 +10191,7 @@
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
@@ -10178,12 +10204,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00067-00</t>
+          <t>P2216-S04-GQC-IR-00056-00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -10194,12 +10220,12 @@
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
         </is>
       </c>
     </row>
@@ -10211,12 +10237,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00094-00</t>
+          <t>P2216-S04-GQC-IR-00078-00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -10232,7 +10258,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
         </is>
       </c>
     </row>
@@ -10244,17 +10270,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00107-00</t>
+          <t>P2216-S04-GQC-IR-00081-00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -10263,7 +10289,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10273,28 +10303,28 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00065-00</t>
+          <t>P2216-S04-GQC-IR-00084-00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CH 04+340 ~ CH 05+415</t>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
         </is>
       </c>
     </row>
@@ -10306,12 +10336,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00070-00</t>
+          <t>P2216-S04-GQC-IR-00087-00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -10325,11 +10355,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>CH 05+415 ~ CH 06+630</t>
-        </is>
-      </c>
+      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10339,30 +10365,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00072-00</t>
+          <t>P2216-S04-GQC-IR-00090-00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>CH 06+630 ~ CH 08+504</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10372,17 +10394,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00073-00</t>
+          <t>P2216-S04-GQC-IR-00035-00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
@@ -10391,11 +10413,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>CH 08+504 ~ CH 09+630</t>
-        </is>
-      </c>
+      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10405,12 +10423,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00074-00</t>
+          <t>P2216-S04-GQC-IR-00039-00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -10426,7 +10444,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CH 09+700 ~ CH 10+640</t>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
         </is>
       </c>
     </row>
@@ -10438,17 +10456,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00099-00</t>
+          <t>P2216-S04-GQC-IR-00043-00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -10457,11 +10475,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>CH 10+640 ~ CH 11+521</t>
-        </is>
-      </c>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10471,12 +10485,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00100-00</t>
+          <t>P2216-S04-GQC-IR-00055-00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -10487,12 +10501,12 @@
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>CH 11+521 ~ CH 12+155</t>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
         </is>
       </c>
     </row>
@@ -10504,17 +10518,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00101-00</t>
+          <t>P2216-S04-GQC-IR-00079-00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -10523,7 +10537,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10533,26 +10551,30 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00102-00</t>
+          <t>P2216-S04-GQC-IR-00082-00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10562,26 +10584,30 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00156-00</t>
+          <t>P2216-S04-GQC-IR-00085-00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10591,17 +10617,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00027-00</t>
+          <t>P2216-S04-GQC-IR-00088-00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -10620,12 +10646,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00038-00</t>
+          <t>P2216-S04-GQC-IR-00091-00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -10636,14 +10662,10 @@
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10653,17 +10675,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00042-00</t>
+          <t>P2216-S04-GQC-IR-00048-00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10672,7 +10694,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>CH 09+532 ~ CH 09+875</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10682,17 +10708,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00056-00</t>
+          <t>P2216-S04-GQC-IR-00052-00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -10703,7 +10729,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
+          <t>CH 10+570 ~ CH 10+913</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10741,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00078-00</t>
+          <t>P2216-S04-GQC-IR-00095-00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10734,11 +10760,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10748,17 +10770,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00081-00</t>
+          <t>P2216-S04-GQC-IR-00096-00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -10767,11 +10789,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
-        </is>
-      </c>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10781,30 +10799,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00084-00</t>
+          <t>P2216-S04-GQC-IR-00097-00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10814,17 +10828,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00087-00</t>
+          <t>P2216-S04-GQC-IR-00122-00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
@@ -10843,12 +10857,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00090-00</t>
+          <t>P2216-S04-GQC-IR-00114-00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10872,12 +10886,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00035-00</t>
+          <t>P2216-S04-GQC-IR-00115-00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10888,10 +10902,14 @@
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10901,17 +10919,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00039-00</t>
+          <t>P2216-S04-GQC-IR-00116-00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
@@ -10920,11 +10938,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
-        </is>
-      </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10934,17 +10948,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00043-00</t>
+          <t>P2216-S04-GQC-IR-00117-00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
@@ -10953,7 +10967,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>CH 10+998 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10963,17 +10981,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00055-00</t>
+          <t>P2216-S04-GQC-IR-00118-00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -10984,7 +11002,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
+          <t>CH 10+720 ~ CH 10+998</t>
         </is>
       </c>
     </row>
@@ -10996,12 +11014,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00079-00</t>
+          <t>P2216-S04-GQC-IR-00123-00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -11015,11 +11033,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11029,12 +11043,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00082-00</t>
+          <t>P2216-S04-GQC-IR-00124-00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -11048,11 +11062,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
-        </is>
-      </c>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11062,30 +11072,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00085-00</t>
+          <t>P2216-S04-GQC-IR-00125-00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11095,17 +11101,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00088-00</t>
+          <t>P2216-S04-GQC-IR-00033-00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -11114,7 +11120,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11124,23 +11134,23 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00091-00</t>
+          <t>P2216-S04-GQC-IR-00026-00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G338" t="inlineStr"/>
@@ -11153,12 +11163,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00048-00</t>
+          <t>P2216-S04-GQC-IR-00046-00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -11172,11 +11182,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>CH 09+532 ~ CH 09+875</t>
-        </is>
-      </c>
+      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11186,12 +11192,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00052-00</t>
+          <t>P2216-S04-GQC-IR-00049-00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -11207,7 +11213,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>CH 10+570 ~ CH 10+913</t>
+          <t>CH 04+250 ~ CH 04+315</t>
         </is>
       </c>
     </row>
@@ -11219,12 +11225,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00095-00</t>
+          <t>P2216-S04-GQC-IR-00110-00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11235,7 +11241,7 @@
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G341" t="inlineStr"/>
@@ -11248,12 +11254,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00096-00</t>
+          <t>P2216-S04-GQC-IR-00111-00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -11264,10 +11270,14 @@
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>CH 11+702 ~ CH 11+737</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11277,26 +11287,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00097-00</t>
+          <t>P2216-S04-GQC-IR-00112-00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>CH 10+935 ~ CH 10+989</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11306,12 +11316,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00122-00</t>
+          <t>P2216-S04-GQC-IR-00113-00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -11320,11 +11330,7 @@
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -11335,12 +11341,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00114-00</t>
+          <t>P2216-S04-GQC-IR-00047-00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11349,12 +11355,12 @@
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11364,12 +11370,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00115-00</t>
+          <t>P2216-S04-GQC-IR-00034-00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11378,16 +11384,8 @@
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160</t>
-        </is>
-      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11397,12 +11395,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00116-00</t>
+          <t>P2216-S04-GQC-IR-00053-00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -11411,11 +11409,7 @@
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
@@ -11426,12 +11420,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00117-00</t>
+          <t>P2216-S04-GQC-IR-00054-00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -11440,14 +11434,10 @@
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
-          <t>CH 10+998 ~ CH 11+525</t>
+          <t>04+250.00 ~ 04+315.00</t>
         </is>
       </c>
     </row>
@@ -11459,12 +11449,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00118-00</t>
+          <t>P2216-S04-GQC-IR-00098-00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -11473,16 +11463,8 @@
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>CH 10+720 ~ CH 10+998</t>
-        </is>
-      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11492,12 +11474,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00123-00</t>
+          <t>P2216-S04-GQC-IR-00119-00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -11506,11 +11488,7 @@
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -11521,12 +11499,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00124-00</t>
+          <t>P2216-S04-GQC-IR-00120-00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11535,11 +11513,7 @@
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -11550,12 +11524,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00125-00</t>
+          <t>P2216-S04-GQC-IR-00121-00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11564,11 +11538,7 @@
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -11579,12 +11549,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00033-00</t>
+          <t>P2216-S04-GQC-IR-00139-00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -11593,16 +11563,8 @@
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11612,12 +11574,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00026-00</t>
+          <t>P2216-S04-GQC-IR-00131-00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -11641,12 +11603,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00046-00</t>
+          <t>P2216-S04-GQC-IR-00132-00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -11670,12 +11632,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00049-00</t>
+          <t>P2216-S04-GQC-IR-00133-00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -11691,7 +11653,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>CH 04+250 ~ CH 04+315</t>
+          <t>CH 11+175 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11665,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00110-00</t>
+          <t>P2216-S04-GQC-IR-00134-00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11719,7 +11681,7 @@
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G357" t="inlineStr"/>
@@ -11732,12 +11694,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00111-00</t>
+          <t>P2216-S04-GQC-IR-00135-00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -11748,14 +11710,10 @@
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>CH 11+702 ~ CH 11+737</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11765,24 +11723,28 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00112-00</t>
+          <t>P2216-S04-GQC-IR-00136-00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>CH 10+935 ~ CH 10+989</t>
+          <t>CH 11+525 ~ CH 11+599</t>
         </is>
       </c>
     </row>
@@ -11794,12 +11756,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00113-00</t>
+          <t>P2216-S04-GQC-IR-00137-00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -11808,7 +11770,11 @@
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -11819,12 +11785,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00047-00</t>
+          <t>P2216-S04-GQC-IR-00037-00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -11833,12 +11799,12 @@
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -11848,12 +11814,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00034-00</t>
+          <t>P2216-S04-GQC-IR-00041-00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -11862,8 +11828,16 @@
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>CH 09+480 ~ CH 09+823</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -11873,12 +11847,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00053-00</t>
+          <t>P2216-S04-GQC-IR-00045-00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -11887,7 +11861,11 @@
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
@@ -11898,12 +11876,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00054-00</t>
+          <t>P2216-S04-GQC-IR-00058-00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -11912,10 +11890,14 @@
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>04+250.00 ~ 04+315.00</t>
+          <t>CH 04+100 ~ CH 04+465</t>
         </is>
       </c>
     </row>
@@ -11927,12 +11909,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00098-00</t>
+          <t>P2216-S04-GQC-IR-00063-00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11941,8 +11923,16 @@
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>CH 10+570 ~ CH 10+913</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11952,12 +11942,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00119-00</t>
+          <t>P2216-S04-GQC-IR-00103-00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -11966,8 +11956,16 @@
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>CH 04+250 ~ CH 11+521</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -11977,12 +11975,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00120-00</t>
+          <t>P2216-S04-GQC-IR-00104-00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -11991,7 +11989,11 @@
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
@@ -12002,12 +12004,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00121-00</t>
+          <t>P2216-S04-GQC-IR-00105-00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -12016,8 +12018,16 @@
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>CH 11+521 ~ CH 12+155</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12027,12 +12037,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00139-00</t>
+          <t>P2216-S04-GQC-IR-00106-00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -12041,7 +12051,11 @@
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
@@ -12052,17 +12066,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>REJ</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00131-00</t>
+          <t>P2216-S04-GQC-IR-00138-00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -12081,12 +12095,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00132-00</t>
+          <t>P2216-S04-GQC-IR-00126-00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -12110,12 +12124,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00133-00</t>
+          <t>P2216-S04-GQC-IR-00127-00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -12131,7 +12145,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>CH 11+175 ~ CH 11+525</t>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
         </is>
       </c>
     </row>
@@ -12143,12 +12157,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00134-00</t>
+          <t>P2216-S04-GQC-IR-00128-00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -12159,7 +12173,7 @@
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G373" t="inlineStr"/>
@@ -12172,12 +12186,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00135-00</t>
+          <t>P2216-S04-GQC-IR-00129-00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -12188,10 +12202,14 @@
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12201,30 +12219,26 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00136-00</t>
+          <t>P2216-S04-GQC-IR-00140-00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 11+599</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12234,23 +12248,23 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00137-00</t>
+          <t>P2216-S04-GQC-IR-00141-00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G376" t="inlineStr"/>
@@ -12263,23 +12277,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00037-00</t>
+          <t>P2216-S04-GQC-IR-00142-00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G377" t="inlineStr"/>
@@ -12292,30 +12306,26 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00041-00</t>
+          <t>P2216-S04-GQC-IR-00143-00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>CH 09+480 ~ CH 09+823</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12325,25 +12335,21 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00045-00</t>
+          <t>P2216-S04-GQC-IR-00162-00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
@@ -12354,28 +12360,24 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00058-00</t>
+          <t>P2216-S04-GQC-IR-00163-00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
-          <t>CH 04+100 ~ CH 04+465</t>
+          <t>12+130</t>
         </is>
       </c>
     </row>
@@ -12387,30 +12389,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00063-00</t>
+          <t>P2216-S04-GQC-IR-00029-00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>CH 10+570 ~ CH 10+913</t>
-        </is>
-      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12420,30 +12414,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00103-00</t>
+          <t>P2216-S04-GQC-IR-00030-00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>CH 04+250 ~ CH 11+521</t>
-        </is>
-      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12453,26 +12439,26 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00104-00</t>
+          <t>P2216-S04-GQC-IR-00031-00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr"/>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>04+250 ~ 04+331.6</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12482,12 +12468,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00105-00</t>
+          <t>P2216-S04-GQC-IR-00155-00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -12495,7 +12481,11 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
       <c r="F384" t="inlineStr">
         <is>
           <t>EXPO</t>
@@ -12503,7 +12493,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>CH 11+521 ~ CH 12+155</t>
+          <t>Qty:5</t>
         </is>
       </c>
     </row>
@@ -12515,12 +12505,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00106-00</t>
+          <t>P2216-S04-GQC-IR-00151-00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -12528,13 +12518,21 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Qty:4</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12544,23 +12542,23 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>REJ</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00138-00</t>
+          <t>P2216-S04-GQC-IR-00158-00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G386" t="inlineStr"/>
@@ -12573,17 +12571,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00126-00</t>
+          <t>P2216-S04-GQC-IR-00160-00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -12592,7 +12590,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>CH 04+425.000 ~ CH 11+521.000</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12602,12 +12604,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00127-00</t>
+          <t>P2216-S04-GQC-IR-00144-00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -12616,16 +12618,8 @@
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
-        </is>
-      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12635,12 +12629,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00128-00</t>
+          <t>P2216-S04-GQC-IR-00145-00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -12649,11 +12643,7 @@
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
@@ -12664,12 +12654,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00129-00</t>
+          <t>P2216-S04-GQC-IR-00146-00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -12683,11 +12673,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -12697,17 +12683,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00140-00</t>
+          <t>P2216-S04-GQC-IR-00147-00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -12716,7 +12702,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>CH 10+763 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -12726,26 +12716,30 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00141-00</t>
+          <t>P2216-S04-GQC-IR-00148-00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12755,25 +12749,21 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00142-00</t>
+          <t>P2216-S04-GQC-IR-00149-00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -12784,25 +12774,21 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00143-00</t>
+          <t>P2216-S04-GQC-IR-00150-00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
@@ -12813,21 +12799,25 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00162-00</t>
+          <t>P2216-S04-GQC-IR-00152-00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -12838,24 +12828,28 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00163-00</t>
+          <t>P2216-S04-GQC-IR-00153-00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>12+130</t>
+          <t>CH 10+763 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -12867,22 +12861,30 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00029-00</t>
+          <t>P2216-S04-GQC-IR-00154-00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -12892,21 +12894,25 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00030-00</t>
+          <t>P2216-S04-GQC-IR-00166-00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -12917,41 +12923,41 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00031-00</t>
+          <t>P2216-S04-GQC-IR-00165-00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>04+250 ~ 04+331.6</t>
-        </is>
-      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00155-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -12961,129 +12967,113 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>Qty:5</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00151-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>Qty:4</t>
-        </is>
-      </c>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00166-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00165-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Sign markers</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00173-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -13091,123 +13081,115 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Sign markers</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00174-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>Expo</t>
-        </is>
-      </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>CH 11+521.000 ~ CH 12+160.000</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Turnout 1st tamping</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00158-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Turnout 2nd tamping</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00160-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>CH 04+425.000 ~ CH 11+521.000</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Turnout 3rd tamping</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00144-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -13215,24 +13197,28 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Turnout Final Tamping</t>
+        </is>
+      </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00145-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -13240,24 +13226,28 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ATW</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00146-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -13265,28 +13255,28 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Turnout de-stressing</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00147-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -13294,115 +13284,115 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>De-streesing of Rail</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00148-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>1stTamping</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00149-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00150-00</t>
+          <t>P2216-S04-GQC-IR-00018-00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr"/>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00152-00</t>
+          <t>P2216-S04-GQC-IR-00019-00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -13410,61 +13400,57 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00153-00</t>
+          <t>P2216-S04-GQC-IR-00000-20</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Control Point</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00154-00</t>
+          <t>P2216-S04-GQC-IR-00021-00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -13472,17 +13458,13 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -13492,12 +13474,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -13507,7 +13489,8 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>Fujairah clearance 
+and fouling marker</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -13521,22 +13504,22 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Structural gauge</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -13550,22 +13533,22 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Track maker</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -13579,12 +13562,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -13594,7 +13577,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing track removal</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -13608,22 +13591,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>buffer stop</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -13632,336 +13615,424 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>HJR19A</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>HJR19B</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>CH 50+942</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>FPJ 01A</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1stTamping</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+          <t>bottom ballast</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>CH 55+043</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+          <t>1st_Tamping</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00000-20</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -13971,66 +14042,81 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+          <t>2nd_Tamping</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Fujairah Clearance And Fouling Marker</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00164-00</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Fujairah clearance 
-and fouling marker</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -14039,27 +14125,27 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Structural Gauge</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Structural gauge</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14068,27 +14154,27 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Track Maker</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Track maker</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14097,27 +14183,27 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Existing track removal</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -14126,17 +14212,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -14146,7 +14232,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>buffer stop</t>
+          <t>existing track ramoval</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -14155,91 +14241,79 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14249,108 +14323,96 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
+          <t>SHA01</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -14360,34 +14422,30 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -14397,34 +14455,30 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -14434,34 +14488,30 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>FinTamping</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -14471,71 +14521,55 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -14545,489 +14579,14 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>2nd_tamping</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>2nd_Tamping</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>Fujairah Port</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Fin_tamping</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>Fin_Tamping</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Existing Track Ramoval</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>existing track ramoval</t>
-        </is>
-      </c>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr"/>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>Existing Track Ramoval</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>existing track ramoval</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr"/>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
-      <c r="G460" t="inlineStr"/>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>SHA01</t>
-        </is>
-      </c>
-      <c r="G461" t="inlineStr"/>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
-      <c r="G462" t="inlineStr"/>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>Turnout Destressing</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>Turnout Destressing</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
-      <c r="G463" t="inlineStr"/>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G466"/>
+  <autoFilter ref="A1:G451"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$447</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-06985-00</t>
+          <t>P2216-PMB-GQC-IR-6985</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -9436,21 +9436,25 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00051-00</t>
+          <t>P2216-S04-GQC-IR-00068-00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>JBL track1</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr"/>
+          <t>Dubai station</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9465,18 +9469,18 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00064-00</t>
+          <t>P2216-S04-GQC-IR-00069-00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>JBL track1</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
@@ -9489,12 +9493,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00068-00</t>
+          <t>P2216-S04-GQC-IR-00050-00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -9505,14 +9509,10 @@
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dubai station</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00069-00</t>
+          <t>P2216-S04-GQC-IR-00059-00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -9538,7 +9538,7 @@
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
@@ -9551,23 +9551,23 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00109-00</t>
+          <t>P2216-S04-GQC-IR-00066-00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>JBL track1</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
@@ -9580,28 +9580,28 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00108-00</t>
+          <t>P2216-S04-GQC-IR-00067-00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>JBL track2</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00050-00</t>
+          <t>P2216-S04-GQC-IR-00094-00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -9632,7 +9632,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9647,12 +9651,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00059-00</t>
+          <t>P2216-S04-GQC-IR-00107-00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -9671,26 +9675,30 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00066-00</t>
+          <t>P2216-S04-GQC-IR-00065-00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dubai station</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>CH 04+340 ~ CH 05+415</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9700,12 +9708,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00067-00</t>
+          <t>P2216-S04-GQC-IR-00070-00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -9716,12 +9724,12 @@
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
+          <t>CH 05+415 ~ CH 06+630</t>
         </is>
       </c>
     </row>
@@ -9733,17 +9741,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00094-00</t>
+          <t>P2216-S04-GQC-IR-00072-00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -9754,7 +9762,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 06+630 ~ CH 08+504</t>
         </is>
       </c>
     </row>
@@ -9766,17 +9774,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00107-00</t>
+          <t>P2216-S04-GQC-IR-00073-00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -9785,7 +9793,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>CH 08+504 ~ CH 09+630</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9800,12 +9812,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00065-00</t>
+          <t>P2216-S04-GQC-IR-00074-00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -9816,7 +9828,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>CH 04+340 ~ CH 05+415</t>
+          <t>CH 09+700 ~ CH 10+640</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9845,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00070-00</t>
+          <t>P2216-S04-GQC-IR-00099-00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -9849,7 +9861,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>CH 05+415 ~ CH 06+630</t>
+          <t>CH 10+640 ~ CH 11+521</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9878,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00072-00</t>
+          <t>P2216-S04-GQC-IR-00100-00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -9877,12 +9889,12 @@
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>CH 06+630 ~ CH 08+504</t>
+          <t>CH 11+521 ~ CH 12+155</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9911,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00073-00</t>
+          <t>P2216-S04-GQC-IR-00101-00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9913,11 +9925,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>CH 08+504 ~ CH 09+630</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9932,7 +9940,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00074-00</t>
+          <t>P2216-S04-GQC-IR-00102-00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9943,14 +9951,10 @@
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>CH 09+700 ~ CH 10+640</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9965,7 +9969,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00099-00</t>
+          <t>P2216-S04-GQC-IR-00156-00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -9979,11 +9983,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>CH 10+640 ~ CH 11+521</t>
-        </is>
-      </c>
+      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9993,30 +9993,26 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00100-00</t>
+          <t>P2216-S04-GQC-IR-00027-00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>CH 11+521 ~ CH 12+155</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10026,12 +10022,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00101-00</t>
+          <t>P2216-S04-GQC-IR-00038-00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -10045,7 +10041,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00102-00</t>
+          <t>P2216-S04-GQC-IR-00042-00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -10071,7 +10071,7 @@
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -10084,17 +10084,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00156-00</t>
+          <t>P2216-S04-GQC-IR-00056-00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -10103,7 +10103,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10118,7 +10122,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00027-00</t>
+          <t>P2216-S04-GQC-IR-00078-00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -10132,7 +10136,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10147,7 +10155,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00038-00</t>
+          <t>P2216-S04-GQC-IR-00081-00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -10163,7 +10171,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10188,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00042-00</t>
+          <t>P2216-S04-GQC-IR-00084-00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -10191,10 +10199,14 @@
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10209,7 +10221,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00056-00</t>
+          <t>P2216-S04-GQC-IR-00087-00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -10223,11 +10235,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
-        </is>
-      </c>
+      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10242,7 +10250,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00078-00</t>
+          <t>P2216-S04-GQC-IR-00090-00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -10253,14 +10261,10 @@
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10270,17 +10274,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00081-00</t>
+          <t>P2216-S04-GQC-IR-00035-00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -10289,11 +10293,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
-        </is>
-      </c>
+      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00084-00</t>
+          <t>P2216-S04-GQC-IR-00039-00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -10319,12 +10319,12 @@
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
         </is>
       </c>
     </row>
@@ -10336,12 +10336,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00087-00</t>
+          <t>P2216-S04-GQC-IR-00043-00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -10365,26 +10365,30 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00090-00</t>
+          <t>P2216-S04-GQC-IR-00055-00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10399,7 +10403,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00035-00</t>
+          <t>P2216-S04-GQC-IR-00079-00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -10413,7 +10417,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10428,12 +10436,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00039-00</t>
+          <t>P2216-S04-GQC-IR-00082-00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
@@ -10444,7 +10452,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10469,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00043-00</t>
+          <t>P2216-S04-GQC-IR-00085-00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -10472,10 +10480,14 @@
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10490,7 +10502,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00055-00</t>
+          <t>P2216-S04-GQC-IR-00088-00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -10504,11 +10516,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
-        </is>
-      </c>
+      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10523,25 +10531,21 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00079-00</t>
+          <t>P2216-S04-GQC-IR-00091-00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10551,12 +10555,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00082-00</t>
+          <t>P2216-S04-GQC-IR-00048-00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -10572,7 +10576,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
+          <t>CH 09+532 ~ CH 09+875</t>
         </is>
       </c>
     </row>
@@ -10584,28 +10588,28 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00085-00</t>
+          <t>P2216-S04-GQC-IR-00052-00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
+          <t>CH 10+570 ~ CH 10+913</t>
         </is>
       </c>
     </row>
@@ -10617,17 +10621,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00088-00</t>
+          <t>P2216-S04-GQC-IR-00095-00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -10646,23 +10650,23 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00091-00</t>
+          <t>P2216-S04-GQC-IR-00096-00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
@@ -10680,7 +10684,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00048-00</t>
+          <t>P2216-S04-GQC-IR-00097-00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -10694,11 +10698,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>CH 09+532 ~ CH 09+875</t>
-        </is>
-      </c>
+      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00052-00</t>
+          <t>P2216-S04-GQC-IR-00122-00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -10727,11 +10727,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>CH 10+570 ~ CH 10+913</t>
-        </is>
-      </c>
+      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10746,7 +10742,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00095-00</t>
+          <t>P2216-S04-GQC-IR-00114-00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10757,7 +10753,7 @@
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
@@ -10775,7 +10771,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00096-00</t>
+          <t>P2216-S04-GQC-IR-00115-00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -10786,10 +10782,14 @@
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00097-00</t>
+          <t>P2216-S04-GQC-IR-00116-00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00122-00</t>
+          <t>P2216-S04-GQC-IR-00117-00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10847,7 +10847,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>CH 10+998 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10862,7 +10866,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00114-00</t>
+          <t>P2216-S04-GQC-IR-00118-00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10873,10 +10877,14 @@
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>CH 10+720 ~ CH 10+998</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10891,7 +10899,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00115-00</t>
+          <t>P2216-S04-GQC-IR-00123-00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10902,14 +10910,10 @@
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10924,7 +10928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00116-00</t>
+          <t>P2216-S04-GQC-IR-00124-00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10953,7 +10957,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00117-00</t>
+          <t>P2216-S04-GQC-IR-00125-00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10967,11 +10971,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>CH 10+998 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00118-00</t>
+          <t>P2216-S04-GQC-IR-00033-00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>CH 10+720 ~ CH 10+998</t>
+          <t>CH 09+630 ~ CH 09+673</t>
         </is>
       </c>
     </row>
@@ -11014,12 +11014,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00123-00</t>
+          <t>P2216-S04-GQC-IR-00026-00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00124-00</t>
+          <t>P2216-S04-GQC-IR-00046-00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00125-00</t>
+          <t>P2216-S04-GQC-IR-00049-00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -11091,7 +11091,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>CH 04+250 ~ CH 04+315</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11106,7 +11110,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00033-00</t>
+          <t>P2216-S04-GQC-IR-00110-00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -11117,14 +11121,10 @@
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00026-00</t>
+          <t>P2216-S04-GQC-IR-00111-00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -11150,10 +11150,14 @@
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>CH 11+702 ~ CH 11+737</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11168,21 +11172,21 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00046-00</t>
+          <t>P2216-S04-GQC-IR-00112-00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>CH 10+935 ~ CH 10+989</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11197,7 +11201,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00049-00</t>
+          <t>P2216-S04-GQC-IR-00113-00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -11206,16 +11210,8 @@
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>CH 04+250 ~ CH 04+315</t>
-        </is>
-      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11225,12 +11221,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00110-00</t>
+          <t>P2216-S04-GQC-IR-00047-00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11239,12 +11235,12 @@
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11254,12 +11250,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00111-00</t>
+          <t>P2216-S04-GQC-IR-00034-00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -11268,16 +11264,8 @@
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>CH 11+702 ~ CH 11+737</t>
-        </is>
-      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11287,26 +11275,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00112-00</t>
+          <t>P2216-S04-GQC-IR-00053-00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>CH 10+935 ~ CH 10+989</t>
-        </is>
-      </c>
+      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11316,12 +11300,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00113-00</t>
+          <t>P2216-S04-GQC-IR-00054-00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -11331,7 +11315,11 @@
       </c>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>04+250.00 ~ 04+315.00</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11346,7 +11334,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00047-00</t>
+          <t>P2216-S04-GQC-IR-00098-00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11356,11 +11344,7 @@
       </c>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11375,7 +11359,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00034-00</t>
+          <t>P2216-S04-GQC-IR-00119-00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11400,7 +11384,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00053-00</t>
+          <t>P2216-S04-GQC-IR-00120-00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -11425,7 +11409,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00054-00</t>
+          <t>P2216-S04-GQC-IR-00121-00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -11435,11 +11419,7 @@
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>04+250.00 ~ 04+315.00</t>
-        </is>
-      </c>
+      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11454,7 +11434,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00098-00</t>
+          <t>P2216-S04-GQC-IR-00139-00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -11474,12 +11454,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00119-00</t>
+          <t>P2216-S04-GQC-IR-00131-00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -11488,7 +11468,11 @@
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -11499,12 +11483,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00120-00</t>
+          <t>P2216-S04-GQC-IR-00132-00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11513,7 +11497,11 @@
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
@@ -11524,12 +11512,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00121-00</t>
+          <t>P2216-S04-GQC-IR-00133-00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11538,8 +11526,16 @@
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>CH 11+175 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11549,12 +11545,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00139-00</t>
+          <t>P2216-S04-GQC-IR-00134-00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -11563,7 +11559,11 @@
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00131-00</t>
+          <t>P2216-S04-GQC-IR-00135-00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00132-00</t>
+          <t>P2216-S04-GQC-IR-00136-00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -11619,10 +11619,14 @@
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 11+599</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11637,7 +11641,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00133-00</t>
+          <t>P2216-S04-GQC-IR-00137-00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -11648,14 +11652,10 @@
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>CH 11+175 ~ CH 11+525</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00134-00</t>
+          <t>P2216-S04-GQC-IR-00037-00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00135-00</t>
+          <t>P2216-S04-GQC-IR-00041-00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -11713,7 +11713,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>CH 09+480 ~ CH 09+823</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11723,12 +11727,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00136-00</t>
+          <t>P2216-S04-GQC-IR-00045-00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -11739,14 +11743,10 @@
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 11+599</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00137-00</t>
+          <t>P2216-S04-GQC-IR-00058-00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -11772,10 +11772,14 @@
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>CH 04+100 ~ CH 04+465</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11790,7 +11794,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00037-00</t>
+          <t>P2216-S04-GQC-IR-00063-00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -11804,7 +11808,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>CH 10+570 ~ CH 10+913</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -11819,7 +11827,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00041-00</t>
+          <t>P2216-S04-GQC-IR-00103-00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -11835,7 +11843,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>CH 09+480 ~ CH 09+823</t>
+          <t>CH 04+250 ~ CH 11+521</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11860,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00045-00</t>
+          <t>P2216-S04-GQC-IR-00104-00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -11881,7 +11889,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00058-00</t>
+          <t>P2216-S04-GQC-IR-00105-00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -11892,12 +11900,12 @@
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>CH 04+100 ~ CH 04+465</t>
+          <t>CH 11+521 ~ CH 12+155</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11922,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00063-00</t>
+          <t>P2216-S04-GQC-IR-00106-00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11925,14 +11933,10 @@
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>CH 10+570 ~ CH 10+913</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11942,17 +11946,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>REJ</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00103-00</t>
+          <t>P2216-S04-GQC-IR-00138-00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -11961,11 +11965,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>CH 04+250 ~ CH 11+521</t>
-        </is>
-      </c>
+      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -11975,12 +11975,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00104-00</t>
+          <t>P2216-S04-GQC-IR-00126-00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00105-00</t>
+          <t>P2216-S04-GQC-IR-00127-00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -12020,12 +12020,12 @@
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>CH 11+521 ~ CH 12+155</t>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
         </is>
       </c>
     </row>
@@ -12037,12 +12037,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00106-00</t>
+          <t>P2216-S04-GQC-IR-00128-00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -12066,26 +12066,30 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>REJ</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00138-00</t>
+          <t>P2216-S04-GQC-IR-00129-00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12095,17 +12099,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00126-00</t>
+          <t>P2216-S04-GQC-IR-00140-00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -12124,17 +12128,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00127-00</t>
+          <t>P2216-S04-GQC-IR-00141-00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -12143,11 +12147,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
-        </is>
-      </c>
+      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12157,17 +12157,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00128-00</t>
+          <t>P2216-S04-GQC-IR-00142-00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -12186,17 +12186,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00129-00</t>
+          <t>P2216-S04-GQC-IR-00143-00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -12205,11 +12205,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12219,12 +12215,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00140-00</t>
+          <t>P2216-S04-GQC-IR-00162-00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -12233,11 +12229,7 @@
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -12248,12 +12240,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00141-00</t>
+          <t>P2216-S04-GQC-IR-00163-00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -12262,12 +12254,12 @@
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>12+130</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12277,25 +12269,21 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00142-00</t>
+          <t>P2216-S04-GQC-IR-00029-00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
@@ -12306,25 +12294,21 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00143-00</t>
+          <t>P2216-S04-GQC-IR-00030-00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
@@ -12335,22 +12319,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00162-00</t>
+          <t>P2216-S04-GQC-IR-00031-00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>04+250 ~ 04+331.6</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12360,24 +12348,32 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00163-00</t>
+          <t>P2216-S04-GQC-IR-00155-00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>12+130</t>
+          <t>Qty:5</t>
         </is>
       </c>
     </row>
@@ -12389,22 +12385,34 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00029-00</t>
+          <t>P2216-S04-GQC-IR-00151-00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>CODE-5</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Qty:4</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12414,21 +12422,25 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00030-00</t>
+          <t>P2216-S04-GQC-IR-00158-00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
@@ -12439,24 +12451,28 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00031-00</t>
+          <t>P2216-S04-GQC-IR-00160-00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>04+250 ~ 04+331.6</t>
+          <t>CH 04+425.000 ~ CH 11+521.000</t>
         </is>
       </c>
     </row>
@@ -12468,12 +12484,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00155-00</t>
+          <t>P2216-S04-GQC-IR-00144-00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -12481,21 +12497,9 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>Qty:5</t>
-        </is>
-      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12505,12 +12509,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00151-00</t>
+          <t>P2216-S04-GQC-IR-00145-00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -12518,21 +12522,9 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Qty:4</t>
-        </is>
-      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12542,17 +12534,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00158-00</t>
+          <t>P2216-S04-GQC-IR-00146-00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -12571,17 +12563,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00160-00</t>
+          <t>P2216-S04-GQC-IR-00147-00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -12592,7 +12584,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>CH 04+425.000 ~ CH 11+521.000</t>
+          <t>CH 10+763 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12601,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00144-00</t>
+          <t>P2216-S04-GQC-IR-00148-00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -12618,8 +12610,16 @@
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00145-00</t>
+          <t>P2216-S04-GQC-IR-00149-00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00146-00</t>
+          <t>P2216-S04-GQC-IR-00150-00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -12668,11 +12668,7 @@
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
@@ -12683,12 +12679,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00147-00</t>
+          <t>P2216-S04-GQC-IR-00152-00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -12699,14 +12695,10 @@
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -12716,12 +12708,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00148-00</t>
+          <t>P2216-S04-GQC-IR-00153-00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -12732,12 +12724,12 @@
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
+          <t>CH 10+763 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12746,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00149-00</t>
+          <t>P2216-S04-GQC-IR-00154-00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -12763,8 +12755,16 @@
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00150-00</t>
+          <t>P2216-S04-GQC-IR-00166-00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -12788,7 +12788,11 @@
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
@@ -12799,23 +12803,23 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00152-00</t>
+          <t>P2216-S04-GQC-IR-00165-00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G395" t="inlineStr"/>
@@ -12823,17 +12827,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00153-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -12841,107 +12845,99 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00154-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
-        </is>
-      </c>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00166-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Ballast MATS</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00165-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
@@ -12952,12 +12948,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -12967,7 +12963,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -12981,22 +12977,22 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -13010,12 +13006,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -13025,7 +13021,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -13039,22 +13035,22 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -13068,12 +13064,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -13083,7 +13079,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -13097,22 +13093,22 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -13126,22 +13122,22 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
+          <t>Turnout de-stressing</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -13155,22 +13151,22 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
+          <t>De-streesing of Rail</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -13184,22 +13180,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>1stTamping</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -13213,22 +13209,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -13242,22 +13238,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00018-00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -13271,12 +13267,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00019-00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -13286,7 +13282,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -13300,22 +13296,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00000-20</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -13329,22 +13325,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>Control Point</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00021-00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>CONTROL POINT</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -13358,22 +13354,23 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Fujairah clearance 
+and fouling marker</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -13387,12 +13384,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -13402,7 +13399,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>Structural gauge</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -13416,22 +13413,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00000-20</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>Track maker</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -13445,12 +13442,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -13460,7 +13457,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>Existing track removal</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -13474,23 +13471,22 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Fujairah Clearance And Fouling Marker</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00164-00</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Fujairah clearance 
-and fouling marker</t>
+          <t>buffer stop</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -13499,118 +13495,150 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Structural Gauge</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>HJR19A</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Track Maker</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Track maker</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
+          <t>Existing Track removal</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>HJR19B</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>CH 50+942</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Existing track removal</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>buffer stop</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -13620,12 +13648,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -13635,12 +13663,12 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>HJR19A</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -13652,7 +13680,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13677,19 +13705,19 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>HJR19B</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 50+942</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13699,7 +13727,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -13714,29 +13742,29 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -13746,34 +13774,34 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 50+200</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -13783,17 +13811,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13805,7 +13833,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -13820,17 +13848,17 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13870,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -13857,7 +13885,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -13867,7 +13895,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13907,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -13894,7 +13922,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -13904,7 +13932,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13944,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -13931,7 +13959,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Fin_Tamping</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -13941,14 +13969,14 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -13958,81 +13986,65 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>CH 55+043</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -14042,56 +14054,40 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -14101,12 +14097,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14116,7 +14112,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>existing track ramoval</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -14130,12 +14126,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -14145,7 +14141,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>existing track ramoval</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14159,25 +14155,29 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -14188,25 +14188,29 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>SHA01</t>
+        </is>
+      </c>
       <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
@@ -14217,12 +14221,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -14232,10 +14236,14 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr"/>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -14246,12 +14254,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -14261,10 +14269,14 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr"/>
+          <t>Turnout Destressing</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
@@ -14275,22 +14287,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -14308,12 +14320,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14323,12 +14335,12 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>SHA01</t>
+          <t>GMC01</t>
         </is>
       </c>
       <c r="G443" t="inlineStr"/>
@@ -14341,22 +14353,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>FinTamping</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -14369,17 +14381,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -14389,63 +14401,55 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -14455,138 +14459,14 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
     </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>LIWA</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Fintamping</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>FinTamping</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G451"/>
+  <autoFilter ref="A1:G447"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00001</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00004</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00003</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00002</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -13695,7 +13695,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -12813,7 +12813,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00000-20</t>
+          <t>P2216-S04-GQC-IR-00020-00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00005</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00006</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -13912,12 +13912,12 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00007</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$447</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$448</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G447"/>
+  <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7984,26 +7984,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07011-00</t>
+          <t>P2216-PMB-GQC-IR-07896-00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>CH 07+861 ~ CH 07+933</t>
-        </is>
-      </c>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8018,7 +8014,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07012-00</t>
+          <t>P2216-PMB-GQC-IR-07011-00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -8030,7 +8026,7 @@
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CH 07+407 ~ CH 07+726</t>
+          <t>CH 07+861 ~ CH 07+933</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8043,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07013-00</t>
+          <t>P2216-PMB-GQC-IR-07012-00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -8059,7 +8055,7 @@
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CH 07+407</t>
+          <t>CH 07+407 ~ CH 07+726</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8084,7 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CH 06+883 ~ CH 06+959</t>
+          <t>CH 07+407</t>
         </is>
       </c>
     </row>
@@ -8105,19 +8101,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07014-00</t>
+          <t>P2216-PMB-GQC-IR-07013-00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>CH 02+590 ~ CH 03+114</t>
+          <t>CH 06+883 ~ CH 06+959</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8130,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07015-00</t>
+          <t>P2216-PMB-GQC-IR-07014-00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -8146,7 +8142,7 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CH 05+355 ~ CH 06+110</t>
+          <t>CH 02+590 ~ CH 03+114</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8159,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07016-00</t>
+          <t>P2216-PMB-GQC-IR-07015-00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -8172,14 +8168,10 @@
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>WESTERN CHORD</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>CH 01+663 ~ CH 02+059</t>
+          <t>CH 05+355 ~ CH 06+110</t>
         </is>
       </c>
     </row>
@@ -8196,19 +8188,23 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07017-00</t>
+          <t>P2216-PMB-GQC-IR-07016-00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>WESTERN CHORD</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>CH 02+590 ~ CH 03+114</t>
+          <t>CH 01+663 ~ CH 02+059</t>
         </is>
       </c>
     </row>
@@ -8220,12 +8216,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06314</t>
+          <t>P2216-PMB-GQC-IR-07017-00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -8234,12 +8230,12 @@
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>MBZ Western Chord</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>CH 02+590 ~ CH 03+114</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8254,7 +8250,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06315</t>
+          <t>P2216-PMB-GQC-IR-06314</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -8268,11 +8264,7 @@
           <t>MBZ Western Chord</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>CH 69+742 ~ CH 69+842</t>
-        </is>
-      </c>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8287,7 +8279,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06316</t>
+          <t>P2216-PMB-GQC-IR-06315</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -8303,7 +8295,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>CH 69+975 ~ CH 70+058</t>
+          <t>CH 69+742 ~ CH 69+842</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8312,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06321</t>
+          <t>P2216-PMB-GQC-IR-06316</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -8331,12 +8323,12 @@
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>MBZ Eastern Chord</t>
+          <t>MBZ Western Chord</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>CH 00+150 ~ CH 00+250</t>
+          <t>CH 69+975 ~ CH 70+058</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8345,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06322</t>
+          <t>P2216-PMB-GQC-IR-06321</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -8369,7 +8361,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>CH 73+721 ~ CH 73+804</t>
+          <t>CH 00+150 ~ CH 00+250</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8378,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06323</t>
+          <t>P2216-PMB-GQC-IR-06322</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -8402,7 +8394,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>CH 73+497 ~ CH 73+580</t>
+          <t>CH 73+721 ~ CH 73+804</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8411,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06324</t>
+          <t>P2216-PMB-GQC-IR-06323</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -8433,7 +8425,11 @@
           <t>MBZ Eastern Chord</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>CH 73+497 ~ CH 73+580</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8448,7 +8444,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06713-00</t>
+          <t>P2216-PMB-GQC-IR-06324</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -8459,7 +8455,7 @@
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>zone -5</t>
+          <t>MBZ Eastern Chord</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
@@ -8477,7 +8473,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06719-00</t>
+          <t>P2216-PMB-GQC-IR-06713-00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -8491,11 +8487,7 @@
           <t>zone -5</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>CH 00+386 ~ CH 08+885</t>
-        </is>
-      </c>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8510,7 +8502,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06748-00</t>
+          <t>P2216-PMB-GQC-IR-06719-00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -8521,12 +8513,12 @@
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>zone -5</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>CH 00+425 ~ CH 02+468</t>
+          <t>CH 00+386 ~ CH 08+885</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8530,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ballastprofiling</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07020-00</t>
+          <t>P2216-PMB-GQC-IR-06748-00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -8554,12 +8546,12 @@
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>western chord</t>
+          <t>West</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>CH 00+425.000 ~ CH 02+468.000</t>
+          <t>CH 00+425 ~ CH 02+468</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8568,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07021-00</t>
+          <t>P2216-PMB-GQC-IR-07020-00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -8585,10 +8577,14 @@
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>western chord</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CH 00+386.000 ~ CH 08+912.000</t>
+          <t>CH 00+425.000 ~ CH 02+468.000</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8601,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07022-00</t>
+          <t>P2216-PMB-GQC-IR-07021-00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8615,7 +8611,11 @@
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>CH 00+386.000 ~ CH 08+912.000</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8625,30 +8625,22 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Ballastprofiling</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07040-00</t>
+          <t>P2216-PMB-GQC-IR-07022-00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>western chrod</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>CH 00+424.000 ~ CH 02+468.000</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8663,7 +8655,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07032-00</t>
+          <t>P2216-PMB-GQC-IR-07040-00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8672,10 +8664,14 @@
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>western chrod</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>CH 00+385.000 ~ CH 02+500.000</t>
+          <t>CH 00+424.000 ~ CH 02+468.000</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8688,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07519-00</t>
+          <t>P2216-PMB-GQC-IR-07032-00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -8702,7 +8698,11 @@
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>CH 00+385.000 ~ CH 02+500.000</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07037-00</t>
+          <t>P2216-PMB-GQC-IR-07519-00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-07038-00</t>
+          <t>P2216-PMB-GQC-IR-07037-00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -8762,25 +8762,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ex track removal</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06125-00</t>
+          <t>P2216-PMB-GQC-IR-07038-00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>MBZ Western Chord</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -8796,7 +8792,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06126-00</t>
+          <t>P2216-PMB-GQC-IR-06125-00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -8810,11 +8806,7 @@
           <t>MBZ Western Chord</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>CH 69+819 ~ CH 69+925</t>
-        </is>
-      </c>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8829,7 +8821,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06128-00</t>
+          <t>P2216-PMB-GQC-IR-06126-00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -8845,7 +8837,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>CH 69+975 ~ CH 70+051</t>
+          <t>CH 69+819 ~ CH 69+925</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8854,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06129-00</t>
+          <t>P2216-PMB-GQC-IR-06128-00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -8873,12 +8865,12 @@
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MBZ Eastern Chord</t>
+          <t>MBZ Western Chord</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>CH 00+044 ~ CH 00+150</t>
+          <t>CH 69+975 ~ CH 70+051</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8887,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06130-00</t>
+          <t>P2216-PMB-GQC-IR-06129-00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8911,7 +8903,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>CH 73+721 ~ CH 73+827</t>
+          <t>CH 00+044 ~ CH 00+150</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8920,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06132-00</t>
+          <t>P2216-PMB-GQC-IR-06130-00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -8942,7 +8934,11 @@
           <t>MBZ Eastern Chord</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>CH 73+721 ~ CH 73+827</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8957,7 +8953,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06131-01</t>
+          <t>P2216-PMB-GQC-IR-06132-00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -8971,11 +8967,7 @@
           <t>MBZ Eastern Chord</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>CH 73+580 ~ CH 73+497</t>
-        </is>
-      </c>
+      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8985,12 +8977,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>Ex track removal</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-06628-00</t>
+          <t>P2216-PMB-GQC-IR-06131-01</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8998,19 +8990,15 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Control Point</t>
-        </is>
-      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>MBZ  Section</t>
+          <t>MBZ Eastern Chord</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Qty：43</t>
+          <t>CH 73+580 ~ CH 73+497</t>
         </is>
       </c>
     </row>
@@ -9022,12 +9010,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>P2216-PMB-GQC-IR-6985</t>
+          <t>P2216-PMB-GQC-IR-06628-00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -9035,9 +9023,21 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>MBZ  Section</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Qty：43</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Sign markers</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07069-00</t>
+          <t>P2216-PMB-GQC-IR-6985</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -9062,11 +9062,7 @@
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>CH 00+386.000 ~ CH 08+912.000</t>
-        </is>
-      </c>
+      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9081,7 +9077,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07070-00</t>
+          <t>P2216-S04-GQC-IR-07069-00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -9091,7 +9087,11 @@
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>CH 00+386.000 ~ CH 08+912.000</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07071-00</t>
+          <t>P2216-S04-GQC-IR-07070-00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -9115,11 +9115,7 @@
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>western chord</t>
-        </is>
-      </c>
+      <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -9130,26 +9126,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Datum plate</t>
+          <t>Sign markers</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07096-00</t>
+          <t>P2216-S04-GQC-IR-07071-00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>CH 02+620.000 ~ CH 07+660.000</t>
-        </is>
-      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>western chord</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9164,36 +9160,36 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-07546-00</t>
+          <t>P2216-S04-GQC-IR-07096-00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>western chord</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>CH 02+620.000 ~ CH 07+660.000</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Ballast mats</t>
+          <t>Datum plate</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00025-00</t>
+          <t>P2216-S04-GQC-IR-07546-00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -9201,14 +9197,10 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>BALLAST MATS</t>
-        </is>
-      </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>JBL TRACK 1</t>
+          <t>western chord</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
@@ -9226,7 +9218,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00075-00</t>
+          <t>P2216-S04-GQC-IR-00025-00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -9241,14 +9233,10 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>JBL TRACK 2</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>CH 11+181.990 ~ CH 11+525.370</t>
-        </is>
-      </c>
+          <t>JBL TRACK 1</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9263,7 +9251,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00023-00</t>
+          <t>P2216-S04-GQC-IR-00075-00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -9278,12 +9266,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
+          <t>JBL TRACK 2</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CH 11+525.370 ~ CH 11+601.760</t>
+          <t>CH 11+181.990 ~ CH 11+525.370</t>
         </is>
       </c>
     </row>
@@ -9300,12 +9288,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00076-00</t>
+          <t>P2216-S04-GQC-IR-00023-00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9315,10 +9303,14 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>JBL TRACK 1</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr"/>
+          <t>EXPO STATION</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>CH 11+525.370 ~ CH 11+601.760</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9333,7 +9325,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00077-00</t>
+          <t>P2216-S04-GQC-IR-00076-00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -9348,7 +9340,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>EXPO STATION</t>
+          <t>JBL TRACK 1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
@@ -9366,12 +9358,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00024-00</t>
+          <t>P2216-S04-GQC-IR-00077-00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9399,12 +9391,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00093-00</t>
+          <t>P2216-S04-GQC-IR-00024-00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9417,11 +9409,7 @@
           <t>EXPO STATION</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>CH 11+887.190 ~ CH 11+979.540</t>
-        </is>
-      </c>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9431,28 +9419,32 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Bottom ballast</t>
+          <t>Ballast mats</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00068-00</t>
+          <t>P2216-S04-GQC-IR-00093-00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr"/>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>BALLAST MATS</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>EXPO STATION</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
+          <t>CH 11+887.190 ~ CH 11+979.540</t>
         </is>
       </c>
     </row>
@@ -9469,12 +9461,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00069-00</t>
+          <t>P2216-S04-GQC-IR-00068-00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -9483,7 +9475,11 @@
           <t>Dubai station</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9493,23 +9489,23 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Bottom ballast</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00050-00</t>
+          <t>P2216-S04-GQC-IR-00069-00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
@@ -9527,12 +9523,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00059-00</t>
+          <t>P2216-S04-GQC-IR-00050-00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -9556,7 +9552,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00066-00</t>
+          <t>P2216-S04-GQC-IR-00059-00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -9567,7 +9563,7 @@
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dubai station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
@@ -9585,7 +9581,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00067-00</t>
+          <t>P2216-S04-GQC-IR-00066-00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -9599,11 +9595,7 @@
           <t>Dubai station</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9618,23 +9610,23 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00094-00</t>
+          <t>P2216-S04-GQC-IR-00067-00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Dubai station</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9643,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00107-00</t>
+          <t>P2216-S04-GQC-IR-00094-00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -9665,7 +9657,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9675,12 +9671,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00065-00</t>
+          <t>P2216-S04-GQC-IR-00107-00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9694,11 +9690,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>CH 04+340 ~ CH 05+415</t>
-        </is>
-      </c>
+      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9713,12 +9705,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00070-00</t>
+          <t>P2216-S04-GQC-IR-00065-00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -9729,7 +9721,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>CH 05+415 ~ CH 06+630</t>
+          <t>CH 04+340 ~ CH 05+415</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9738,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00072-00</t>
+          <t>P2216-S04-GQC-IR-00070-00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9762,7 +9754,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CH 06+630 ~ CH 08+504</t>
+          <t>CH 05+415 ~ CH 06+630</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9771,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00073-00</t>
+          <t>P2216-S04-GQC-IR-00072-00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9795,7 +9787,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>CH 08+504 ~ CH 09+630</t>
+          <t>CH 06+630 ~ CH 08+504</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9804,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00074-00</t>
+          <t>P2216-S04-GQC-IR-00073-00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -9828,7 +9820,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>CH 09+700 ~ CH 10+640</t>
+          <t>CH 08+504 ~ CH 09+630</t>
         </is>
       </c>
     </row>
@@ -9845,12 +9837,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00099-00</t>
+          <t>P2216-S04-GQC-IR-00074-00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -9861,7 +9853,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>CH 10+640 ~ CH 11+521</t>
+          <t>CH 09+700 ~ CH 10+640</t>
         </is>
       </c>
     </row>
@@ -9878,23 +9870,23 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00100-00</t>
+          <t>P2216-S04-GQC-IR-00099-00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>CH 11+521 ~ CH 12+155</t>
+          <t>CH 10+640 ~ CH 11+521</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9903,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00101-00</t>
+          <t>P2216-S04-GQC-IR-00100-00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9922,10 +9914,14 @@
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>CH 11+521 ~ CH 12+155</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9940,7 +9936,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00102-00</t>
+          <t>P2216-S04-GQC-IR-00101-00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9951,7 +9947,7 @@
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr"/>
@@ -9969,18 +9965,18 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00156-00</t>
+          <t>P2216-S04-GQC-IR-00102-00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
@@ -9993,12 +9989,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00027-00</t>
+          <t>P2216-S04-GQC-IR-00156-00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -10027,12 +10023,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00038-00</t>
+          <t>P2216-S04-GQC-IR-00027-00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -10041,11 +10037,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
-        </is>
-      </c>
+      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10060,7 +10052,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00042-00</t>
+          <t>P2216-S04-GQC-IR-00038-00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -10074,7 +10066,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10089,7 +10085,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00056-00</t>
+          <t>P2216-S04-GQC-IR-00042-00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -10103,11 +10099,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
-        </is>
-      </c>
+      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10122,12 +10114,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00078-00</t>
+          <t>P2216-S04-GQC-IR-00056-00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -10138,7 +10130,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
         </is>
       </c>
     </row>
@@ -10155,12 +10147,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00081-00</t>
+          <t>P2216-S04-GQC-IR-00078-00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -10171,7 +10163,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10180,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00084-00</t>
+          <t>P2216-S04-GQC-IR-00081-00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -10199,12 +10191,12 @@
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10213,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00087-00</t>
+          <t>P2216-S04-GQC-IR-00084-00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -10232,10 +10224,14 @@
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10250,18 +10246,18 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00090-00</t>
+          <t>P2216-S04-GQC-IR-00087-00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
@@ -10274,12 +10270,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00035-00</t>
+          <t>P2216-S04-GQC-IR-00090-00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -10290,7 +10286,7 @@
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
@@ -10308,12 +10304,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00039-00</t>
+          <t>P2216-S04-GQC-IR-00035-00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
@@ -10322,11 +10318,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>CH 09+480.000 ~ CH 09+823.195</t>
-        </is>
-      </c>
+      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10341,7 +10333,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00043-00</t>
+          <t>P2216-S04-GQC-IR-00039-00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -10355,7 +10347,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>CH 09+480.000 ~ CH 09+823.195</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10370,7 +10366,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00055-00</t>
+          <t>P2216-S04-GQC-IR-00043-00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -10384,11 +10380,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>CH 04+100.000 ~ CH 04+465.000</t>
-        </is>
-      </c>
+      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10403,12 +10395,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00079-00</t>
+          <t>P2216-S04-GQC-IR-00055-00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
@@ -10419,7 +10411,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>CH 04+250.000 ~ CH 10+100.000</t>
+          <t>CH 04+100.000 ~ CH 04+465.000</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10428,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00082-00</t>
+          <t>P2216-S04-GQC-IR-00079-00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -10452,7 +10444,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CH 10+100.000 ~ CH 11+520.000</t>
+          <t>CH 04+250.000 ~ CH 10+100.000</t>
         </is>
       </c>
     </row>
@@ -10469,23 +10461,23 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00085-00</t>
+          <t>P2216-S04-GQC-IR-00082-00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CH 11+520.000 ~ CH 12+155.097</t>
+          <t>CH 10+100.000 ~ CH 11+520.000</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10494,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00088-00</t>
+          <t>P2216-S04-GQC-IR-00085-00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -10513,10 +10505,14 @@
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>CH 11+520.000 ~ CH 12+155.097</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10531,7 +10527,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00091-00</t>
+          <t>P2216-S04-GQC-IR-00088-00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -10542,7 +10538,7 @@
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G318" t="inlineStr"/>
@@ -10555,30 +10551,26 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00048-00</t>
+          <t>P2216-S04-GQC-IR-00091-00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>CH 09+532 ~ CH 09+875</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10593,7 +10585,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00052-00</t>
+          <t>P2216-S04-GQC-IR-00048-00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -10609,7 +10601,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>CH 10+570 ~ CH 10+913</t>
+          <t>CH 09+532 ~ CH 09+875</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10618,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00095-00</t>
+          <t>P2216-S04-GQC-IR-00052-00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -10640,7 +10632,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>CH 10+570 ~ CH 10+913</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10655,7 +10651,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00096-00</t>
+          <t>P2216-S04-GQC-IR-00095-00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -10684,7 +10680,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00097-00</t>
+          <t>P2216-S04-GQC-IR-00096-00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -10713,7 +10709,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00122-00</t>
+          <t>P2216-S04-GQC-IR-00097-00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -10742,7 +10738,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00114-00</t>
+          <t>P2216-S04-GQC-IR-00122-00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10753,7 +10749,7 @@
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
@@ -10771,7 +10767,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00115-00</t>
+          <t>P2216-S04-GQC-IR-00114-00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -10785,11 +10781,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 12+160</t>
-        </is>
-      </c>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10804,7 +10796,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00116-00</t>
+          <t>P2216-S04-GQC-IR-00115-00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10815,10 +10807,14 @@
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10833,7 +10829,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00117-00</t>
+          <t>P2216-S04-GQC-IR-00116-00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10847,11 +10843,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>CH 10+998 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10866,7 +10858,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00118-00</t>
+          <t>P2216-S04-GQC-IR-00117-00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10882,7 +10874,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>CH 10+720 ~ CH 10+998</t>
+          <t>CH 10+998 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10891,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00123-00</t>
+          <t>P2216-S04-GQC-IR-00118-00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10913,7 +10905,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>CH 10+720 ~ CH 10+998</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10928,7 +10924,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00124-00</t>
+          <t>P2216-S04-GQC-IR-00123-00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10957,7 +10953,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00125-00</t>
+          <t>P2216-S04-GQC-IR-00124-00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10981,12 +10977,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Turnout installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00033-00</t>
+          <t>P2216-S04-GQC-IR-00125-00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -11000,11 +10996,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11019,7 +11011,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00026-00</t>
+          <t>P2216-S04-GQC-IR-00033-00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -11033,7 +11025,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11048,7 +11044,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00046-00</t>
+          <t>P2216-S04-GQC-IR-00026-00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -11077,7 +11073,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00049-00</t>
+          <t>P2216-S04-GQC-IR-00046-00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -11091,11 +11087,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>CH 04+250 ~ CH 04+315</t>
-        </is>
-      </c>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11110,7 +11102,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00110-00</t>
+          <t>P2216-S04-GQC-IR-00049-00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -11121,10 +11113,14 @@
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>CH 04+250 ~ CH 04+315</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11139,7 +11135,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00111-00</t>
+          <t>P2216-S04-GQC-IR-00110-00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -11153,11 +11149,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>CH 11+702 ~ CH 11+737</t>
-        </is>
-      </c>
+      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11172,7 +11164,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00112-00</t>
+          <t>P2216-S04-GQC-IR-00111-00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -11181,10 +11173,14 @@
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>CH 10+935 ~ CH 10+989</t>
+          <t>CH 11+702 ~ CH 11+737</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11197,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00113-00</t>
+          <t>P2216-S04-GQC-IR-00112-00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -11211,7 +11207,11 @@
       </c>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>CH 10+935 ~ CH 10+989</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout installation</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00047-00</t>
+          <t>P2216-S04-GQC-IR-00113-00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11236,11 +11236,7 @@
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>CH 09+630 ~ CH 09+673</t>
-        </is>
-      </c>
+      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11255,7 +11251,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00034-00</t>
+          <t>P2216-S04-GQC-IR-00047-00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -11265,7 +11261,11 @@
       </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>CH 09+630 ~ CH 09+673</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00053-00</t>
+          <t>P2216-S04-GQC-IR-00034-00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00054-00</t>
+          <t>P2216-S04-GQC-IR-00053-00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -11315,11 +11315,7 @@
       </c>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>04+250.00 ~ 04+315.00</t>
-        </is>
-      </c>
+      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11334,7 +11330,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00098-00</t>
+          <t>P2216-S04-GQC-IR-00054-00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11344,7 +11340,11 @@
       </c>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>04+250.00 ~ 04+315.00</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00119-00</t>
+          <t>P2216-S04-GQC-IR-00098-00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00120-00</t>
+          <t>P2216-S04-GQC-IR-00119-00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00121-00</t>
+          <t>P2216-S04-GQC-IR-00120-00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00139-00</t>
+          <t>P2216-S04-GQC-IR-00121-00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -11454,12 +11454,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>GR Installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00131-00</t>
+          <t>P2216-S04-GQC-IR-00139-00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -11468,11 +11468,7 @@
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>JBL</t>
-        </is>
-      </c>
+      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
@@ -11488,7 +11484,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00132-00</t>
+          <t>P2216-S04-GQC-IR-00131-00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11517,7 +11513,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00133-00</t>
+          <t>P2216-S04-GQC-IR-00132-00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11531,11 +11527,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>CH 11+175 ~ CH 11+525</t>
-        </is>
-      </c>
+      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11550,7 +11542,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00134-00</t>
+          <t>P2216-S04-GQC-IR-00133-00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -11564,7 +11556,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>CH 11+175 ~ CH 11+525</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11579,7 +11575,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00135-00</t>
+          <t>P2216-S04-GQC-IR-00134-00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -11608,7 +11604,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00136-00</t>
+          <t>P2216-S04-GQC-IR-00135-00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -11619,14 +11615,10 @@
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>CH 11+525 ~ CH 11+599</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11641,7 +11633,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00137-00</t>
+          <t>P2216-S04-GQC-IR-00136-00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -11655,7 +11647,11 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 11+599</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11665,12 +11661,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Final tamping</t>
+          <t>GR Installation</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00037-00</t>
+          <t>P2216-S04-GQC-IR-00137-00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11681,7 +11677,7 @@
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G357" t="inlineStr"/>
@@ -11699,7 +11695,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00041-00</t>
+          <t>P2216-S04-GQC-IR-00037-00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -11713,11 +11709,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>CH 09+480 ~ CH 09+823</t>
-        </is>
-      </c>
+      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11732,7 +11724,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00045-00</t>
+          <t>P2216-S04-GQC-IR-00041-00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -11746,7 +11738,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>CH 09+480 ~ CH 09+823</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11761,7 +11757,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00058-00</t>
+          <t>P2216-S04-GQC-IR-00045-00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -11775,11 +11771,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>CH 04+100 ~ CH 04+465</t>
-        </is>
-      </c>
+      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11794,7 +11786,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00063-00</t>
+          <t>P2216-S04-GQC-IR-00058-00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -11810,7 +11802,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>CH 10+570 ~ CH 10+913</t>
+          <t>CH 04+100 ~ CH 04+465</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11819,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00103-00</t>
+          <t>P2216-S04-GQC-IR-00063-00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -11843,7 +11835,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>CH 04+250 ~ CH 11+521</t>
+          <t>CH 10+570 ~ CH 10+913</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11852,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00104-00</t>
+          <t>P2216-S04-GQC-IR-00103-00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -11874,7 +11866,11 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>CH 04+250 ~ CH 11+521</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -11889,7 +11885,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00105-00</t>
+          <t>P2216-S04-GQC-IR-00104-00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -11900,14 +11896,10 @@
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>CH 11+521 ~ CH 12+155</t>
-        </is>
-      </c>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -11922,7 +11914,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00106-00</t>
+          <t>P2216-S04-GQC-IR-00105-00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -11936,7 +11928,11 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>CH 11+521 ~ CH 12+155</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11946,23 +11942,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>REJ</t>
+          <t>Final tamping</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00138-00</t>
+          <t>P2216-S04-GQC-IR-00106-00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G366" t="inlineStr"/>
@@ -11975,17 +11971,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Ballast profiling</t>
+          <t>REJ</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00126-00</t>
+          <t>P2216-S04-GQC-IR-00138-00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -12009,7 +12005,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00127-00</t>
+          <t>P2216-S04-GQC-IR-00126-00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -12023,11 +12019,7 @@
           <t>JBL</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>CH 10+720.000 ~ CH 11+525.378</t>
-        </is>
-      </c>
+      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12042,7 +12034,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00128-00</t>
+          <t>P2216-S04-GQC-IR-00127-00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -12053,10 +12045,14 @@
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>CH 10+720.000 ~ CH 11+525.378</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12071,7 +12067,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00129-00</t>
+          <t>P2216-S04-GQC-IR-00128-00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -12085,11 +12081,7 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>CH 11+525.378 ~ CH 12+160.115</t>
-        </is>
-      </c>
+      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12099,26 +12091,30 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Rail flaw detection</t>
+          <t>Ballast profiling</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00140-00</t>
+          <t>P2216-S04-GQC-IR-00129-00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr"/>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>CH 11+525.378 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12133,7 +12129,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00141-00</t>
+          <t>P2216-S04-GQC-IR-00140-00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -12162,7 +12158,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00142-00</t>
+          <t>P2216-S04-GQC-IR-00141-00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -12173,7 +12169,7 @@
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G373" t="inlineStr"/>
@@ -12191,7 +12187,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00143-00</t>
+          <t>P2216-S04-GQC-IR-00142-00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -12215,12 +12211,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Rail flaw detection</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00162-00</t>
+          <t>P2216-S04-GQC-IR-00143-00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -12229,7 +12225,11 @@
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
       <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00163-00</t>
+          <t>P2216-S04-GQC-IR-00162-00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -12255,11 +12255,7 @@
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>12+130</t>
-        </is>
-      </c>
+      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12269,22 +12265,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Existing track removal (JBL</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00029-00</t>
+          <t>P2216-S04-GQC-IR-00163-00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>12+130</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00030-00</t>
+          <t>P2216-S04-GQC-IR-00029-00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00031-00</t>
+          <t>P2216-S04-GQC-IR-00030-00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -12334,11 +12334,7 @@
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>04+250 ~ 04+331.6</t>
-        </is>
-      </c>
+      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12348,32 +12344,24 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SURVEY WORK</t>
+          <t>Existing track removal (JBL</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00155-00</t>
+          <t>P2216-S04-GQC-IR-00031-00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>control point</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Qty:5</t>
+          <t>04+250 ~ 04+331.6</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12378,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00151-00</t>
+          <t>P2216-S04-GQC-IR-00155-00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -12405,12 +12393,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Qty:4</t>
+          <t>Qty:5</t>
         </is>
       </c>
     </row>
@@ -12422,26 +12410,34 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Structure gauge inspection</t>
+          <t>SURVEY WORK</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00158-00</t>
+          <t>P2216-S04-GQC-IR-00151-00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr"/>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>control point</t>
+        </is>
+      </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>EXPO</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr"/>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Qty:4</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12456,25 +12452,21 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00160-00</t>
+          <t>P2216-S04-GQC-IR-00158-00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>CH 04+425.000 ~ CH 11+521.000</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12484,22 +12476,30 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>DTS 1st</t>
+          <t>Structure gauge inspection</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00144-00</t>
+          <t>P2216-S04-GQC-IR-00160-00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>CH 04+425.000 ~ CH 11+521.000</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00145-00</t>
+          <t>P2216-S04-GQC-IR-00144-00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00146-00</t>
+          <t>P2216-S04-GQC-IR-00145-00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -12548,11 +12548,7 @@
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
@@ -12568,7 +12564,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00147-00</t>
+          <t>P2216-S04-GQC-IR-00146-00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -12579,14 +12575,10 @@
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12601,7 +12593,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00148-00</t>
+          <t>P2216-S04-GQC-IR-00147-00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -12612,12 +12604,12 @@
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
+          <t>CH 10+763 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -12629,12 +12621,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DTS 2nd</t>
+          <t>DTS 1st</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00149-00</t>
+          <t>P2216-S04-GQC-IR-00148-00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -12643,8 +12635,16 @@
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00150-00</t>
+          <t>P2216-S04-GQC-IR-00149-00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00152-00</t>
+          <t>P2216-S04-GQC-IR-00150-00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -12693,11 +12693,7 @@
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>EXPO</t>
-        </is>
-      </c>
+      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
@@ -12713,7 +12709,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00153-00</t>
+          <t>P2216-S04-GQC-IR-00152-00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -12724,14 +12720,10 @@
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
-          <t>JBL</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>CH 10+763 ~ CH 11+525</t>
-        </is>
-      </c>
+          <t>EXPO</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12746,7 +12738,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00154-00</t>
+          <t>P2216-S04-GQC-IR-00153-00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -12757,12 +12749,12 @@
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>CH 11+525 ~ CH 12+160.115</t>
+          <t>CH 10+763 ~ CH 11+525</t>
         </is>
       </c>
     </row>
@@ -12774,12 +12766,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Fouling point</t>
+          <t>DTS 2nd</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00166-00</t>
+          <t>P2216-S04-GQC-IR-00154-00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -12793,7 +12785,11 @@
           <t>EXPO</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>CH 11+525 ~ CH 12+160.115</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -12808,7 +12804,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00165-00</t>
+          <t>P2216-S04-GQC-IR-00166-00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -12819,7 +12815,7 @@
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="G395" t="inlineStr"/>
@@ -12827,17 +12823,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fouling point</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-00165-00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -12845,12 +12841,12 @@
           <t>CODE-1</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
       <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
@@ -12861,22 +12857,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -12895,12 +12891,12 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -12919,22 +12915,22 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -12948,12 +12944,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -12963,7 +12959,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -12977,22 +12973,22 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -13006,12 +13002,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -13021,7 +13017,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -13035,12 +13031,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -13050,7 +13046,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -13064,22 +13060,22 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -13093,12 +13089,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -13108,7 +13104,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -13122,12 +13118,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -13137,7 +13133,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -13151,12 +13147,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -13166,7 +13162,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>Turnout de-stressing</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -13180,22 +13176,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>De-streesing of Rail</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -13209,12 +13205,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -13224,7 +13220,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>1stTamping</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -13238,12 +13234,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -13253,7 +13249,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -13267,22 +13263,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00018-00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -13296,12 +13292,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00019-00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -13311,7 +13307,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -13325,12 +13321,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00020-00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -13340,7 +13336,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -13354,54 +13350,54 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
     </row>
@@ -13413,12 +13409,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Track Maker</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -13428,7 +13424,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Track maker</t>
+          <t>Structural gauge</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -13442,12 +13438,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -13457,7 +13453,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Existing track removal</t>
+          <t>Track maker</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -13471,22 +13467,22 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>buffer stop</t>
+          <t>Existing track removal</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -13495,39 +13491,31 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -13542,7 +13530,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -13557,12 +13545,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>HJR19B</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>CH 50+942</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
@@ -13574,12 +13562,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -13589,17 +13577,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
@@ -13611,12 +13599,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -13626,7 +13614,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -13636,7 +13624,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CH 50+200</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
@@ -13648,12 +13636,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -13663,7 +13651,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -13673,44 +13661,44 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00001</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13710,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00004</t>
+          <t>P2435-FJP-GQC-IR-00001</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -13737,17 +13725,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13759,12 +13747,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00003</t>
+          <t>P2435-FJP-GQC-IR-00004</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -13774,7 +13762,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -13801,7 +13789,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00002</t>
+          <t>P2435-FJP-GQC-IR-00003</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -13821,7 +13809,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13821,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00005</t>
+          <t>P2435-FJP-GQC-IR-00002</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -13848,7 +13836,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -13870,12 +13858,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00006</t>
+          <t>P2435-FJP-GQC-IR-00005</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -13885,7 +13873,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -13895,7 +13883,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13907,12 +13895,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00007</t>
+          <t>P2435-FJP-GQC-IR-00006</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -13922,7 +13910,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -13944,22 +13932,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00007</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -13976,31 +13964,39 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -14015,7 +14011,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -14044,7 +14040,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -14068,12 +14064,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -14083,7 +14079,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -14097,12 +14093,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14112,7 +14108,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -14131,7 +14127,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -14155,12 +14151,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -14170,14 +14166,10 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -14193,12 +14185,12 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -14208,7 +14200,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>SHA01</t>
+          <t>GMC01</t>
         </is>
       </c>
       <c r="G439" t="inlineStr"/>
@@ -14221,27 +14213,27 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G440" t="inlineStr"/>
@@ -14254,12 +14246,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -14269,7 +14261,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -14287,22 +14279,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -14320,12 +14312,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14335,7 +14327,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -14353,12 +14345,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -14368,7 +14360,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>FinTamping</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -14381,30 +14373,34 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr"/>
+          <t>FinTamping</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
@@ -14415,22 +14411,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -14449,12 +14445,12 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -14465,8 +14461,37 @@
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
     </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G447"/>
+  <autoFilter ref="A1:G448"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$448</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$450</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G448"/>
+  <dimension ref="A1:G450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13705,37 +13705,37 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00001</t>
+          <t>P2435-HJR-GQC-IR-0039-00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>FPJ 01A</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 48+921</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00004</t>
+          <t>P2435-FJP-GQC-IR-00001</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -13762,17 +13762,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FPJ 01A</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 55+002</t>
         </is>
       </c>
     </row>
@@ -13784,12 +13784,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00003</t>
+          <t>P2435-FJP-GQC-IR-00004</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00002</t>
+          <t>P2435-FJP-GQC-IR-00003</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 55+543</t>
         </is>
       </c>
     </row>
@@ -13858,12 +13858,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00005</t>
+          <t>P2435-FJP-GQC-IR-00002</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>bottom ballast</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00006</t>
+          <t>P2435-FJP-GQC-IR-00005</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 55+043</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>1st_tamping</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00007</t>
+          <t>P2435-FJP-GQC-IR-00006</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
+          <t>1st_Tamping</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -13969,22 +13969,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>2nd_tamping</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-FJP-GQC-IR-00007</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
+          <t>2nd_Tamping</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -14001,60 +14001,76 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fin_tamping</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+          <t>Fin_Tamping</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>CH 55+002</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Port</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2435-FJP-GQC-IR-00008</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>未匹配到对应code</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>FJP</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>CH 55+543</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -14069,7 +14085,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -14093,12 +14109,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14108,7 +14124,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -14122,12 +14138,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -14137,7 +14153,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14151,12 +14167,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -14166,7 +14182,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14180,12 +14196,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -14195,14 +14211,10 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
@@ -14213,29 +14225,25 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>SHA01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -14246,12 +14254,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -14261,7 +14269,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -14279,27 +14287,27 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G442" t="inlineStr"/>
@@ -14312,22 +14320,22 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -14345,22 +14353,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -14378,12 +14386,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -14393,7 +14401,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>FinTamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -14406,59 +14414,67 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr"/>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr"/>
+          <t>FinTamping</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -14469,29 +14485,87 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
     </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G448"/>
+  <autoFilter ref="A1:G450"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$449</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G450"/>
+  <dimension ref="A1:G449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12852,17 +12852,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-0177</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -12872,84 +12872,96 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>PMB06</t>
+        </is>
+      </c>
       <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-0178</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>PMB07</t>
+        </is>
+      </c>
       <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-0179</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr"/>
+          <t>1st tamping</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>PMB06</t>
+        </is>
+      </c>
       <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-0180</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -12959,26 +12971,30 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr"/>
+          <t>2nd tamping</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>PBM06</t>
+        </is>
+      </c>
       <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-0181</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -12988,97 +13004,113 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>MFBW</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr"/>
+          <t>1st tamping</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>PMB07</t>
+        </is>
+      </c>
       <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-0182</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr"/>
+          <t>2nd tamping</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>PMB07</t>
+        </is>
+      </c>
       <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-0183</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr"/>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>PMB07</t>
+        </is>
+      </c>
       <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-0184</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr"/>
+          <t>Destressing</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>PMB07</t>
+        </is>
+      </c>
       <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
@@ -13089,12 +13121,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -13104,7 +13136,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -13118,22 +13150,22 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -13147,22 +13179,22 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -13176,12 +13208,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -13191,7 +13223,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -13205,22 +13237,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -13234,12 +13266,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -13249,7 +13281,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -13263,12 +13295,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -13278,7 +13310,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -13292,22 +13324,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -13321,12 +13353,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -13336,7 +13368,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -13350,12 +13382,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -13365,7 +13397,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -13379,370 +13411,322 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
+          <t>Turnout De-stressing</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00014-00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Turnout de-stressing</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>De-streesing Of Rail</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00015-00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>De-streesing of Rail</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1sttamping</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00016-00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>1stTamping</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00017-00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>2nd Tamping</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00018-00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00019-00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>Track maker</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>Existing track removal</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>buffer stop</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Track Laying</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Fujairah Loop</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Ballast Mat</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>ballast mat</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>Structural gauge</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0039-00</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>MFBW</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>CH 48+921</t>
-        </is>
-      </c>
+          <t>Track maker</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13752,145 +13736,129 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00001</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>FPJ 01A</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>CH 55+002</t>
-        </is>
-      </c>
+          <t>Existing track removal</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00004</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00003</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 55+543</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>bottom ballast</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -13900,12 +13868,12 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00005</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -13915,103 +13883,103 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 55+043</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>1st_tamping</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00006</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>1st_Tamping</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2nd_tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00007</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2nd_Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Fin_tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2435-HJR-GQC-IR-0039-00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -14021,56 +13989,48 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Fin_Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>HJR</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CH 55+002</t>
+          <t>CH 48+921</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Fujairah Port</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2435-FJP-GQC-IR-00008</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>MFBW</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>FJP</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>CH 55+543</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -14085,7 +14045,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -14114,7 +14074,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14138,12 +14098,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -14153,7 +14113,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14167,12 +14127,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -14182,7 +14142,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>existing track ramoval</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14201,7 +14161,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -14225,12 +14185,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -14240,10 +14200,14 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -14259,12 +14223,12 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -14274,7 +14238,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G441" t="inlineStr"/>
@@ -14287,27 +14251,27 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>SHA01</t>
+          <t>GMC01</t>
         </is>
       </c>
       <c r="G442" t="inlineStr"/>
@@ -14320,12 +14284,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14335,7 +14299,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -14353,22 +14317,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -14386,12 +14350,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -14401,7 +14365,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -14419,12 +14383,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -14434,7 +14398,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>FinTamping</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -14447,34 +14411,30 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>PL-28</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>FinTamping</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
@@ -14485,22 +14445,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2216-DMB-GQC-IR-00328</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -14519,12 +14479,12 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -14535,37 +14495,8 @@
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>PL-28</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G450"/>
+  <autoFilter ref="A1:G449"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$449</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$453</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G449"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -12880,7 +12880,11 @@
           <t>PMB06</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>CH 04+549</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -12900,7 +12904,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -12913,7 +12917,11 @@
           <t>PMB07</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>CH 04+599</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -12933,7 +12941,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -12946,7 +12954,11 @@
           <t>PMB06</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>CH 04+399</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -12966,7 +12978,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -12979,7 +12991,11 @@
           <t>PBM06</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>CH 04+399</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -12999,7 +13015,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13012,7 +13028,11 @@
           <t>PMB07</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>CH 04+449</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13032,7 +13052,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -13045,7 +13065,11 @@
           <t>PMB07</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>CH 04+349</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -13065,7 +13089,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -13078,7 +13102,11 @@
           <t>PMB07</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>CH 04+599</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13098,7 +13126,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13111,51 +13139,63 @@
           <t>PMB07</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>CH 04+499</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-0185</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>PMB06</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>CH 04+549</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-0186</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -13165,69 +13205,93 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
+          <t>Destressing</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>PMB06</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>CH 04+449</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Fin Tamping</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-0187</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
+          <t>fin tamping</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>PMB06</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>CH 04+399</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-0188</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr"/>
+          <t>fintamping</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>PMB07</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>CH 04+449</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13237,12 +13301,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -13252,7 +13316,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -13266,22 +13330,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -13295,12 +13359,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -13310,7 +13374,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -13324,22 +13388,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -13353,12 +13417,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -13368,7 +13432,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -13382,22 +13446,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -13411,22 +13475,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -13440,22 +13504,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -13469,22 +13533,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -13498,22 +13562,22 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -13527,22 +13591,22 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Turnout de-stressing</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -13556,12 +13620,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -13571,7 +13635,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>De-streesing of Rail</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -13585,22 +13649,22 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>1stTamping</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -13614,22 +13678,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -13643,291 +13707,259 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00018-00</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00019-00</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
+      <c r="C427" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>Track maker</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>Existing track removal</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>buffer stop</t>
-        </is>
-      </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>Structural gauge</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
+          <t>Track maker</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
+          <t>Existing track removal</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>ballast mat</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -13937,12 +13969,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -13952,12 +13984,12 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -13974,12 +14006,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0039-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -13989,24 +14021,24 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CH 48+921</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14016,108 +14048,140 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2435-HJR-GQC-IR-0039-00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>CH 48+921</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -14127,12 +14191,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -14142,7 +14206,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14156,12 +14220,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -14171,7 +14235,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -14185,12 +14249,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -14200,14 +14264,10 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -14218,29 +14278,25 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>SHA01</t>
-        </is>
-      </c>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
@@ -14251,12 +14307,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -14266,14 +14322,10 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
@@ -14284,12 +14336,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14299,14 +14351,10 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -14317,22 +14365,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -14350,27 +14398,27 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G445" t="inlineStr"/>
@@ -14383,22 +14431,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>FinTamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -14411,17 +14459,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -14431,72 +14479,204 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr"/>
+          <t>Turnout Destressing</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr"/>
+          <t>1st Tamping</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00260</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>CODE-4</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Fintamping</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00261</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>CODE-4</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>FinTamping</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
           <t>PL-28</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00360</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr">
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
         <is>
           <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr">
+      <c r="D453" t="inlineStr">
         <is>
           <t>UR</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr">
+      <c r="E453" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G449"/>
+  <autoFilter ref="A1:G453"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -12900,7 +12900,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$474</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$478</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00210</t>
+          <t>P2216-S04-GQC-IR-0210</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00211</t>
+          <t>P2216-S04-GQC-IR-0211</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -14069,118 +14069,150 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-0212</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>PMB04E</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>CH 04+372</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-0213</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+          <t>Destressing</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>PMB04E</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>CH 04+272</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-0214</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+          <t>ATW</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>PMB05</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>CH 04+427</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-0215</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+          <t>Destressing</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>PMB05</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>CH 04+515</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -14190,12 +14222,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -14205,7 +14237,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -14219,22 +14251,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -14248,12 +14280,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -14263,7 +14295,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -14277,22 +14309,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14306,12 +14338,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -14321,7 +14353,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14335,22 +14367,22 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -14364,22 +14396,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -14393,22 +14425,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -14422,22 +14454,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -14451,22 +14483,22 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -14480,22 +14512,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>Turnout de-stressing</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -14509,12 +14541,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -14524,7 +14556,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>De-streesing of Rail</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -14538,22 +14570,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>1stTamping</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -14567,22 +14599,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -14596,291 +14628,259 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00018-00</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>CODE-5</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>3rd Tamping</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00019-00</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Final Tamping</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr">
+      <c r="C452" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>Track maker</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Existing Track Removal</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>Existing track removal</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Buffer Stop</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>CODE-2</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>buffer stop</t>
-        </is>
-      </c>
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>Structural gauge</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G454" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
+          <t>Track maker</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Track laying</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>CH 48+927</t>
-        </is>
-      </c>
+          <t>Existing track removal</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>ballast mat</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>HJR</t>
-        </is>
-      </c>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>CH 50+200</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -14905,12 +14905,12 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -14927,12 +14927,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0039-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -14942,24 +14942,24 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>CH 48+921</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14969,108 +14969,140 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr"/>
+          <t>Track laying</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>CH 48+927</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr"/>
+          <t>ballast mat</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>CH 50+200</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr"/>
-      <c r="G461" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2435-HJR-GQC-IR-0039-00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr"/>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>CH 48+921</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -15080,12 +15112,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -15095,7 +15127,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -15109,12 +15141,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -15124,7 +15156,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -15138,12 +15170,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -15153,14 +15185,10 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
@@ -15171,29 +15199,25 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>SHA01</t>
-        </is>
-      </c>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr"/>
     </row>
     <row r="467">
@@ -15204,12 +15228,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -15219,14 +15243,10 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>ATW</t>
-        </is>
-      </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr"/>
     </row>
     <row r="468">
@@ -15237,12 +15257,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -15252,14 +15272,10 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
-        </is>
-      </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr"/>
     </row>
     <row r="469">
@@ -15270,22 +15286,22 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -15303,27 +15319,27 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G470" t="inlineStr"/>
@@ -15336,22 +15352,22 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>FinTamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -15364,17 +15380,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -15384,72 +15400,204 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr"/>
+          <t>Turnout Destressing</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr"/>
+          <t>1st Tamping</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00260</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>CODE-4</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>LIWA</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Fintamping</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>P2414-GMC-GQC-IR-00261</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>CODE-4</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>FinTamping</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
           <t>PL-28</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Track Laying</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00360</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>CODE-2</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>TRACK LAYING</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
         <is>
           <t>P2216-DMB-GQC-IR-00359</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr">
+      <c r="D478" t="inlineStr">
         <is>
           <t>UR</t>
         </is>
       </c>
-      <c r="E474" t="inlineStr">
+      <c r="E478" t="inlineStr">
         <is>
           <t>Bottom Ballast</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G474"/>
+  <autoFilter ref="A1:G478"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -13566,7 +13566,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$478</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$480</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G478"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14217,46 +14217,54 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Fouling Point</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-0216</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+          <t>fouling point</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Rahayel Depot</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Track Removal</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-0217</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -14266,11 +14274,19 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+          <t>Track removal</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Rahayel Depot</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -14280,22 +14296,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -14309,22 +14325,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -14338,22 +14354,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14367,22 +14383,22 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -14396,22 +14412,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -14425,12 +14441,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -14440,7 +14456,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -14454,22 +14470,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -14483,22 +14499,22 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -14512,12 +14528,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -14527,7 +14543,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -14541,12 +14557,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -14556,7 +14572,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -14570,22 +14586,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>Turnout de-stressing</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -14599,22 +14615,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>De-streesing of Rail</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -14628,12 +14644,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -14643,7 +14659,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>1stTamping</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -14657,22 +14673,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -14686,22 +14702,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00018-00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -14715,12 +14731,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00019-00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -14730,7 +14746,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -14744,83 +14760,83 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
+      <c r="C454" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>Track maker</t>
-        </is>
-      </c>
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr"/>
     </row>
@@ -14832,12 +14848,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -14847,7 +14863,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Existing track removal</t>
+          <t>Structural gauge</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -14861,22 +14877,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>buffer stop</t>
+          <t>Track maker</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -14885,7 +14901,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -14895,66 +14911,50 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>Existing track removal</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -14964,12 +14964,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -14979,17 +14979,17 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
@@ -15001,12 +15001,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -15016,17 +15016,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>CH 50+200</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
@@ -15038,12 +15038,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
@@ -15075,12 +15075,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0039-00</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -15100,67 +15100,83 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>CH 48+921</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2435-HJR-GQC-IR-0039-00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>CH 48+921</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -15175,7 +15191,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -15199,12 +15215,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -15214,7 +15230,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -15228,12 +15244,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -15243,7 +15259,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -15257,12 +15273,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -15272,7 +15288,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -15286,12 +15302,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -15301,14 +15317,10 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
@@ -15319,29 +15331,25 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F470" t="inlineStr">
-        <is>
-          <t>SHA01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr"/>
     </row>
     <row r="471">
@@ -15352,12 +15360,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -15367,7 +15375,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -15385,27 +15393,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G472" t="inlineStr"/>
@@ -15418,22 +15426,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -15451,22 +15459,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -15484,12 +15492,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -15499,7 +15507,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>FinTamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -15512,59 +15520,67 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr"/>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr"/>
+          <t>FinTamping</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
@@ -15575,29 +15591,87 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr"/>
     </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G478"/>
+  <autoFilter ref="A1:G480"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITR Status" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ITR Status'!$A$1:$G$482</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G480"/>
+  <dimension ref="A1:G482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>P2225-PS4-GQC-IR-04380-00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>未匹配到对应code</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -12885,7 +12885,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12922,7 +12922,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -12959,7 +12959,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12996,7 +12996,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13033,7 +13033,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -13070,7 +13070,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13107,7 +13107,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -13144,7 +13144,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -13181,7 +13181,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -13218,7 +13218,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -13255,7 +13255,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -13292,7 +13292,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -13329,7 +13329,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13403,7 +13403,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13440,7 +13440,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -13477,7 +13477,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -13588,7 +13588,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -13625,7 +13625,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -13662,7 +13662,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -13699,7 +13699,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -13736,7 +13736,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -13773,7 +13773,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -13847,7 +13847,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13884,7 +13884,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13921,7 +13921,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13958,7 +13958,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13995,7 +13995,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -14032,7 +14032,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -14069,7 +14069,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -14106,7 +14106,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -14143,7 +14143,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -14180,7 +14180,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -14217,7 +14217,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>MBZ</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -14291,46 +14291,54 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00004-00</t>
+          <t>P2216-S04-GQC-IR-0218</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Rahayel Depot</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Fujairah Station</t>
+          <t>MBZ Station</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Ballast Profilling</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00005-00</t>
+          <t>P2216-S04-GQC-IR-0219</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -14340,10 +14348,14 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr"/>
+          <t>ballast profilling</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Rahayel Depot</t>
+        </is>
+      </c>
       <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
@@ -14354,22 +14366,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00157-00</t>
+          <t>P2216-S04-GQC-IR-00004-00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Ballast MATS</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -14383,22 +14395,22 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00006-00</t>
+          <t>P2216-S04-GQC-IR-00005-00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -14412,22 +14424,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00008-00</t>
+          <t>P2216-S04-GQC-IR-00157-00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast MATS</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -14441,22 +14453,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Turnout 1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00009-00</t>
+          <t>P2216-S04-GQC-IR-00006-00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Turnout 1st tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -14470,22 +14482,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Turnout 2nd Tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00010-00</t>
+          <t>P2216-S04-GQC-IR-00008-00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Turnout 2nd tamping</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -14499,12 +14511,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Turnout 3rd Tamping</t>
+          <t>Turnout 1st Tamping</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00011-00</t>
+          <t>P2216-S04-GQC-IR-00009-00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -14514,7 +14526,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Turnout 3rd tamping</t>
+          <t>Turnout 1st tamping</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -14528,22 +14540,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Turnout 2nd Tamping</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00012-00</t>
+          <t>P2216-S04-GQC-IR-00010-00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Turnout Final Tamping</t>
+          <t>Turnout 2nd tamping</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -14557,22 +14569,22 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 3rd Tamping</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00013-00</t>
+          <t>P2216-S04-GQC-IR-00011-00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout 3rd tamping</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -14586,12 +14598,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Turnout De-stressing</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00014-00</t>
+          <t>P2216-S04-GQC-IR-00012-00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -14601,7 +14613,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Turnout de-stressing</t>
+          <t>Turnout Final Tamping</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -14615,12 +14627,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>De-streesing Of Rail</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00015-00</t>
+          <t>P2216-S04-GQC-IR-00013-00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -14630,7 +14642,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>De-streesing of Rail</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -14644,22 +14656,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>1sttamping</t>
+          <t>Turnout De-stressing</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00016-00</t>
+          <t>P2216-S04-GQC-IR-00014-00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>1stTamping</t>
+          <t>Turnout de-stressing</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -14673,22 +14685,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>De-streesing Of Rail</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00017-00</t>
+          <t>P2216-S04-GQC-IR-00015-00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>CODE-5</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>De-streesing of Rail</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -14702,12 +14714,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>1sttamping</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00018-00</t>
+          <t>P2216-S04-GQC-IR-00016-00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -14717,7 +14729,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>3rd Tamping</t>
+          <t>1stTamping</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -14731,22 +14743,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00019-00</t>
+          <t>P2216-S04-GQC-IR-00017-00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Final Tamping</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -14760,22 +14772,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00020-00</t>
+          <t>P2216-S04-GQC-IR-00018-00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-5</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Ballast Profilling</t>
+          <t>3rd Tamping</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -14789,12 +14801,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Control Point</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00021-00</t>
+          <t>P2216-S04-GQC-IR-00019-00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -14804,7 +14816,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>CONTROL POINT</t>
+          <t>Final Tamping</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -14818,83 +14830,83 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00020-00</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Ballast Profilling</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Control Point</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>P2216-S04-GQC-IR-00021-00</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>CONTROL POINT</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Fujairah Station</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
           <t>Fujairah Clearance And Fouling Marker</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
+      <c r="C456" t="inlineStr">
         <is>
           <t>P2216-S04-GQC-IR-00164-00</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>CODE-1</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
         <is>
           <t>Fujairah clearance 
 and fouling marker</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Structural Gauge</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00168-00</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>Structural gauge</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>Fujairah Station</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Track Maker</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>P2216-S04-GQC-IR-00170-00</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>CODE-1</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>Track maker</t>
-        </is>
-      </c>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
     </row>
@@ -14906,12 +14918,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Structural Gauge</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00171-00</t>
+          <t>P2216-S04-GQC-IR-00168-00</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -14921,7 +14933,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Existing track removal</t>
+          <t>Structural gauge</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -14935,22 +14947,22 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Buffer Stop</t>
+          <t>Track Maker</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-00130-00</t>
+          <t>P2216-S04-GQC-IR-00170-00</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>buffer stop</t>
+          <t>Track maker</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -14959,7 +14971,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14969,66 +14981,50 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0034-00</t>
+          <t>P2216-S04-GQC-IR-00171-00</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>HJR19A</t>
-        </is>
-      </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>CH 48+887</t>
-        </is>
-      </c>
+          <t>Existing track removal</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Fujairah Loop</t>
+          <t>Fujairah Station</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Existing Track Removal</t>
+          <t>Buffer Stop</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>P2216-S04-GQC-IR-00130-00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Existing Track removal</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>HJR19B</t>
-        </is>
-      </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>CH 50+942</t>
-        </is>
-      </c>
+          <t>buffer stop</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -15038,12 +15034,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0036-00</t>
+          <t>P2435-HJR-GQC-IR-0034-00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -15053,17 +15049,17 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Track laying</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19A</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>CH 48+927</t>
+          <t>CH 48+887</t>
         </is>
       </c>
     </row>
@@ -15075,12 +15071,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Ballast Mat</t>
+          <t>Existing Track Removal</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0035-00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -15090,17 +15086,17 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>ballast mat</t>
+          <t>Existing Track removal</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>HJR</t>
+          <t>HJR19B</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>CH 50+200</t>
+          <t>CH 50+942</t>
         </is>
       </c>
     </row>
@@ -15112,12 +15108,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0037-00</t>
+          <t>P2435-HJR-GQC-IR-0036-00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -15127,7 +15123,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Track laying</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -15137,7 +15133,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>CH 48+887</t>
+          <t>CH 48+927</t>
         </is>
       </c>
     </row>
@@ -15149,12 +15145,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>Ballast Mat</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>P2435-HJR-GQC-IR-0039-00</t>
+          <t>P2435-HJR-GQC-IR-0035-00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -15164,7 +15160,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>MFBW</t>
+          <t>ballast mat</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -15174,67 +15170,83 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>CH 48+921</t>
+          <t>CH 50+200</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00243</t>
+          <t>P2435-HJR-GQC-IR-0037-00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr"/>
+          <t>Turnout Installation</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>CH 48+887</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>LIWA</t>
+          <t>Fujairah Loop</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>MFBW</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00251</t>
+          <t>P2435-HJR-GQC-IR-0039-00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr"/>
+          <t>MFBW</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>HJR</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>CH 48+921</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -15249,7 +15261,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00253</t>
+          <t>P2414-GMC-GQC-IR-00243</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -15273,12 +15285,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00244</t>
+          <t>P2414-GMC-GQC-IR-00251</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -15288,7 +15300,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -15302,12 +15314,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00245</t>
+          <t>P2414-GMC-GQC-IR-00253</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -15317,7 +15329,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -15331,12 +15343,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Existing Track Ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00254</t>
+          <t>P2414-GMC-GQC-IR-00244</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -15346,7 +15358,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>existing track ramoval</t>
+          <t>Bottom Ballast</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -15360,12 +15372,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00247</t>
+          <t>P2414-GMC-GQC-IR-00245</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -15375,14 +15387,10 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>GMC01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr"/>
     </row>
     <row r="472">
@@ -15393,29 +15401,25 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>Existing Track Ramoval</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00256</t>
+          <t>P2414-GMC-GQC-IR-00254</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>SHA01</t>
-        </is>
-      </c>
+          <t>existing track ramoval</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
@@ -15426,12 +15430,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00257</t>
+          <t>P2414-GMC-GQC-IR-00247</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -15441,7 +15445,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -15459,27 +15463,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00258</t>
+          <t>P2414-GMC-GQC-IR-00256</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Turnout Destressing</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>GMC01</t>
+          <t>SHA01</t>
         </is>
       </c>
       <c r="G474" t="inlineStr"/>
@@ -15492,22 +15496,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00259</t>
+          <t>P2414-GMC-GQC-IR-00257</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -15525,22 +15529,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00260</t>
+          <t>P2414-GMC-GQC-IR-00258</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>2rd Tamping</t>
+          <t>Turnout Destressing</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -15558,12 +15562,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>P2414-GMC-GQC-IR-00261</t>
+          <t>P2414-GMC-GQC-IR-00259</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -15573,7 +15577,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>FinTamping</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -15586,59 +15590,67 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Track Laying</t>
+          <t>2rd Tamping</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00360</t>
+          <t>P2414-GMC-GQC-IR-00260</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>TRACK LAYING</t>
-        </is>
-      </c>
-      <c r="F478" t="inlineStr"/>
+          <t>2rd Tamping</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>PL-28</t>
+          <t>LIWA</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00328</t>
+          <t>P2414-GMC-GQC-IR-00261</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
-        </is>
-      </c>
-      <c r="F479" t="inlineStr"/>
+          <t>FinTamping</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>GMC01</t>
+        </is>
+      </c>
       <c r="G479" t="inlineStr"/>
     </row>
     <row r="480">
@@ -15649,29 +15661,87 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>Track Laying</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>P2216-DMB-GQC-IR-00359</t>
+          <t>P2216-DMB-GQC-IR-00360</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Bottom Ballast</t>
+          <t>TRACK LAYING</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr"/>
     </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00328</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>PL-28</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>P2216-DMB-GQC-IR-00359</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Bottom Ballast</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G480"/>
+  <autoFilter ref="A1:G482"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CH 12+813 ~ CH 12+867</t>
+          <t>CH 12+813 ~ 12867.00</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-4</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -12885,451 +12885,451 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0177</t>
+          <t>P2216-S04-GQC-IR-0189</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>PMB06</t>
+          <t>PMB04A</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>CH 04+549</t>
+          <t>CH 03+910</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0178</t>
+          <t>P2216-S04-GQC-IR-0190</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>PMB07</t>
+          <t>PMB04A</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>CH 04+599</t>
+          <t>CH 03+910</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Fin Tamping</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0179</t>
+          <t>P2216-S04-GQC-IR-0191</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>fin tamping</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>PMB06</t>
+          <t>PMB04A</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>CH 04+399</t>
+          <t>CH 03+910</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0180</t>
+          <t>P2216-S04-GQC-IR-0202</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>PBM06</t>
+          <t>PMB04A</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>CH 04+399</t>
+          <t>CH 04+063</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0181</t>
+          <t>P2216-S04-GQC-IR-0208</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>PMB07</t>
+          <t>PMB04A</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>CH 04+449</t>
+          <t>CH 04+063</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0182</t>
+          <t>P2216-S04-GQC-IR-0205</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>PMB07</t>
+          <t>PMB04A</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>CH 04+349</t>
+          <t>CH 04+063</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0183</t>
+          <t>P2216-S04-GQC-IR-0192</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>PMB07</t>
+          <t>PMB04B</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>CH 04+599</t>
+          <t>CH 03+965</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0184</t>
+          <t>P2216-S04-GQC-IR-0193</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>PMB07</t>
+          <t>PMB04B</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>CH 04+499</t>
+          <t>CH 03+965</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Fin Tamping</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0185</t>
+          <t>P2216-S04-GQC-IR-0194</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>fin tamping</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>PMB06</t>
+          <t>PMB04B</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>CH 04+549</t>
+          <t>CH 03+965</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0186</t>
+          <t>P2216-S04-GQC-IR-0203</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>PMB06</t>
+          <t>PMB04B</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>CH 04+449</t>
+          <t>CH 04+118</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Fin Tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0187</t>
+          <t>P2216-S04-GQC-IR-0206</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>fin tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>PMB06</t>
+          <t>PMB04B</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>CH 04+399</t>
+          <t>CH 04+118</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Fintamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0188</t>
+          <t>P2216-S04-GQC-IR-0207</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>fintamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>PMB07</t>
+          <t>PMB04B</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>CH 04+449</t>
+          <t>CH 04+118</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -13339,12 +13339,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0189</t>
+          <t>P2216-S04-GQC-IR-0195</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -13354,19 +13354,19 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>PMB04A</t>
+          <t>PMB04E</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>CH 03+910</t>
+          <t>CH 04+220</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0190</t>
+          <t>P2216-S04-GQC-IR-0196</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13391,19 +13391,19 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>PMB04A</t>
+          <t>PMB04E</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>CH 03+910</t>
+          <t>CH 04+220</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0191</t>
+          <t>P2216-S04-GQC-IR-0197</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13428,130 +13428,130 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>PMB04A</t>
+          <t>PMB04E</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>CH 03+910</t>
+          <t>CH 04+220</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0192</t>
+          <t>P2216-S04-GQC-IR-0210</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>PMB04B</t>
+          <t>PMB04E</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>CH 03+965</t>
+          <t>CH 04+372</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0193</t>
+          <t>P2216-S04-GQC-IR-0212</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>PMB04B</t>
+          <t>PMB04E</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>CH 03+965</t>
+          <t>CH 04+372</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Fin Tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0194</t>
+          <t>P2216-S04-GQC-IR-0213</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>fin tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>PMB04B</t>
+          <t>PMB04E</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>CH 03+965</t>
+          <t>CH 04+272</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0195</t>
+          <t>P2216-S04-GQC-IR-0198</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13576,19 +13576,19 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>PMB04E</t>
+          <t>PMB05</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>CH 04+220</t>
+          <t>CH 04+275</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0196</t>
+          <t>P2216-S04-GQC-IR-0199</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13613,19 +13613,19 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>PMB04E</t>
+          <t>PMB05</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>CH 04+220</t>
+          <t>CH 04+275</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0197</t>
+          <t>P2216-S04-GQC-IR-0200</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -13650,39 +13650,39 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>PMB04E</t>
+          <t>PMB05</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>CH 04+220</t>
+          <t>CH 04+275</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>1st Tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0198</t>
+          <t>P2216-S04-GQC-IR-0211</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>1st tamping</t>
+          <t>Turnout Installation</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -13692,34 +13692,34 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>CH 04+275</t>
+          <t>CH 04+427</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2nd Tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0199</t>
+          <t>P2216-S04-GQC-IR-0214</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2nd tamping</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -13729,34 +13729,34 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>CH 04+275</t>
+          <t>CH 04+427</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Fin Tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0200</t>
+          <t>P2216-S04-GQC-IR-0215</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>fin tamping</t>
+          <t>Destressing</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -13766,14 +13766,14 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>CH 04+275</t>
+          <t>CH 04+515</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0202</t>
+          <t>P2216-S04-GQC-IR-0177</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13798,93 +13798,93 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>PMB04A</t>
+          <t>PMB06</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CH 04+063</t>
+          <t>CH 04+549</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0203</t>
+          <t>P2216-S04-GQC-IR-0179</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>PMB04B</t>
+          <t>PMB06</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CH 04+118</t>
+          <t>CH 04+399</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0208</t>
+          <t>P2216-S04-GQC-IR-0180</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>PMB04A</t>
+          <t>PBM06</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>CH 04+063</t>
+          <t>CH 04+399</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13894,12 +13894,12 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0205</t>
+          <t>P2216-S04-GQC-IR-0185</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13909,93 +13909,93 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>PMB04A</t>
+          <t>PMB06</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>CH 04+063</t>
+          <t>CH 04+549</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0206</t>
+          <t>P2216-S04-GQC-IR-0186</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>ATW</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>PMB04B</t>
+          <t>PMB06</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CH 04+118</t>
+          <t>CH 04+449</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>Fin Tamping</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0207</t>
+          <t>P2216-S04-GQC-IR-0187</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>fin tamping</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>PMB04B</t>
+          <t>PMB06</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CH 04+118</t>
+          <t>CH 04+399</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -14005,12 +14005,12 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0210</t>
+          <t>P2216-S04-GQC-IR-0178</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -14020,93 +14020,93 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>PMB04E</t>
+          <t>PMB07</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>CH 04+372</t>
+          <t>CH 04+599</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st Tamping</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0211</t>
+          <t>P2216-S04-GQC-IR-0181</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Turnout Installation</t>
+          <t>1st tamping</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>PMB05</t>
+          <t>PMB07</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>CH 04+427</t>
+          <t>CH 04+449</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd Tamping</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0212</t>
+          <t>P2216-S04-GQC-IR-0182</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>ATW</t>
+          <t>2nd tamping</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>PMB04E</t>
+          <t>PMB07</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CH 04+372</t>
+          <t>CH 04+349</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0213</t>
+          <t>P2216-S04-GQC-IR-0183</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -14131,19 +14131,19 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>PMB04E</t>
+          <t>PMB07</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>CH 04+272</t>
+          <t>CH 04+599</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0214</t>
+          <t>P2216-S04-GQC-IR-0184</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -14168,56 +14168,56 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>PMB05</t>
+          <t>PMB07</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>CH 04+427</t>
+          <t>CH 04+499</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>Fintamping</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P2216-S04-GQC-IR-0215</t>
+          <t>P2216-S04-GQC-IR-0188</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Destressing</t>
+          <t>fintamping</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>PMB05</t>
+          <t>PMB07</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CH 04+515</t>
+          <t>CH 04+449</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -14291,7 +14291,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -14328,7 +14328,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MBZ Station</t>
+          <t>Rahayel Depot</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">

--- a/ITR_Status_Report.xlsx
+++ b/ITR_Status_Report.xlsx
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>CODE-2</t>
+          <t>CODE-1</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CODE-4</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>CODE-2</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CODE-1</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
